--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1992" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1287ADBB-6F3C-4A38-9639-EDD5BAA7DDAC}"/>
+  <xr:revisionPtr revIDLastSave="2028" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96826851-0233-461D-A805-6804E36EDE61}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="2" r:id="rId1"/>
@@ -19,13 +19,14 @@
     <sheet name="2023" sheetId="5" r:id="rId4"/>
     <sheet name="2024" sheetId="6" r:id="rId5"/>
     <sheet name="2025" sheetId="7" r:id="rId6"/>
+    <sheet name="2026" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10387" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10428" uniqueCount="502">
   <si>
     <t>Year</t>
   </si>
@@ -1519,6 +1520,18 @@
   </si>
   <si>
     <t>Overturned</t>
+  </si>
+  <si>
+    <t>FP2</t>
+  </si>
+  <si>
+    <t>Performed practice start outside designated practice area</t>
+  </si>
+  <si>
+    <t>Nish Shetty, Pedro Lamy, Mathieu Remmerie, Matthew Selley</t>
+  </si>
+  <si>
+    <t>Car having mechanical problems</t>
   </si>
 </sst>
 </file>
@@ -1603,6 +1616,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -45655,4 +45672,166 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
+  <dimension ref="A1:P4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="11" max="11" width="22.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2026</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" t="s">
+        <v>498</v>
+      </c>
+      <c r="G2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J2" t="s">
+        <v>91</v>
+      </c>
+      <c r="O2" t="s">
+        <v>499</v>
+      </c>
+      <c r="P2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2026</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" t="s">
+        <v>498</v>
+      </c>
+      <c r="G3" t="s">
+        <v>274</v>
+      </c>
+      <c r="I3" t="s">
+        <v>331</v>
+      </c>
+      <c r="J3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2026</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F4" t="s">
+        <v>498</v>
+      </c>
+      <c r="G4" t="s">
+        <v>278</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>285</v>
+      </c>
+      <c r="O4" t="s">
+        <v>501</v>
+      </c>
+      <c r="P4" t="s">
+        <v>500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2028" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96826851-0233-461D-A805-6804E36EDE61}"/>
+  <xr:revisionPtr revIDLastSave="2031" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{886FA6FA-5E46-4CBA-91A0-342848161262}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45679,6 +45679,9 @@
   <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="7" max="7" width="32.21875" customWidth="1"/>
+    <col min="8" max="8" width="31" customWidth="1"/>
+    <col min="9" max="9" width="22.6640625" customWidth="1"/>
     <col min="11" max="11" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2031" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{886FA6FA-5E46-4CBA-91A0-342848161262}"/>
+  <xr:revisionPtr revIDLastSave="2063" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9023412C-8D97-455F-97B9-71E8EDEFEC86}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10428" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10454" uniqueCount="507">
   <si>
     <t>Year</t>
   </si>
@@ -1532,6 +1532,21 @@
   </si>
   <si>
     <t>Car having mechanical problems</t>
+  </si>
+  <si>
+    <t>Duct cooling fan left attached to vehicle</t>
+  </si>
+  <si>
+    <t>Left front wheel assembly</t>
+  </si>
+  <si>
+    <t>Working on car in the fast lane</t>
+  </si>
+  <si>
+    <t>Team member did not touch vehicle while in fast lane</t>
+  </si>
+  <si>
+    <t>Collision in pit lane</t>
   </si>
 </sst>
 </file>
@@ -45676,7 +45691,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -45795,6 +45810,9 @@
       <c r="J3" t="s">
         <v>84</v>
       </c>
+      <c r="O3" t="s">
+        <v>506</v>
+      </c>
       <c r="P3" t="s">
         <v>500</v>
       </c>
@@ -45831,6 +45849,111 @@
         <v>501</v>
       </c>
       <c r="P4" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>2026</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" t="s">
+        <v>236</v>
+      </c>
+      <c r="J5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>7500</v>
+      </c>
+      <c r="O5" t="s">
+        <v>502</v>
+      </c>
+      <c r="P5" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>2026</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" t="s">
+        <v>236</v>
+      </c>
+      <c r="J6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>5000</v>
+      </c>
+      <c r="O6" t="s">
+        <v>503</v>
+      </c>
+      <c r="P6" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2026</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" t="s">
+        <v>274</v>
+      </c>
+      <c r="H7" t="s">
+        <v>504</v>
+      </c>
+      <c r="J7" t="s">
+        <v>285</v>
+      </c>
+      <c r="O7" t="s">
+        <v>505</v>
+      </c>
+      <c r="P7" t="s">
         <v>500</v>
       </c>
     </row>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2063" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9023412C-8D97-455F-97B9-71E8EDEFEC86}"/>
+  <xr:revisionPtr revIDLastSave="2111" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48DBA661-180D-4FE8-89CC-F54C65640100}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10454" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10503" uniqueCount="514">
   <si>
     <t>Year</t>
   </si>
@@ -1547,6 +1547,27 @@
   </si>
   <si>
     <t>Collision in pit lane</t>
+  </si>
+  <si>
+    <t>Audi</t>
+  </si>
+  <si>
+    <t>Start Procedure Infringement</t>
+  </si>
+  <si>
+    <t>Car did not reach grid under own power</t>
+  </si>
+  <si>
+    <t>Grid Procedure Infringement</t>
+  </si>
+  <si>
+    <t>Stop-and-Go</t>
+  </si>
+  <si>
+    <t>Team member touching car after 15 second signal</t>
+  </si>
+  <si>
+    <t>Cadillac</t>
   </si>
 </sst>
 </file>
@@ -1631,10 +1652,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -45691,7 +45708,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -45957,6 +45974,201 @@
         <v>500</v>
       </c>
     </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>2026</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>507</v>
+      </c>
+      <c r="F8" t="s">
+        <v>222</v>
+      </c>
+      <c r="G8" t="s">
+        <v>508</v>
+      </c>
+      <c r="J8" t="s">
+        <v>285</v>
+      </c>
+      <c r="O8" t="s">
+        <v>509</v>
+      </c>
+      <c r="P8" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2026</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G9" t="s">
+        <v>510</v>
+      </c>
+      <c r="J9" t="s">
+        <v>511</v>
+      </c>
+      <c r="O9" t="s">
+        <v>512</v>
+      </c>
+      <c r="P9" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>2026</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" t="s">
+        <v>266</v>
+      </c>
+      <c r="I10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" t="s">
+        <v>285</v>
+      </c>
+      <c r="O10" t="s">
+        <v>301</v>
+      </c>
+      <c r="P10" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>2026</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>152</v>
+      </c>
+      <c r="F11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" t="s">
+        <v>266</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" t="s">
+        <v>285</v>
+      </c>
+      <c r="O11" t="s">
+        <v>301</v>
+      </c>
+      <c r="P11" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>2026</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" t="s">
+        <v>278</v>
+      </c>
+      <c r="J12" t="s">
+        <v>285</v>
+      </c>
+      <c r="P12" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>2026</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" t="s">
+        <v>513</v>
+      </c>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I13" t="s">
+        <v>197</v>
+      </c>
+      <c r="J13" t="s">
+        <v>285</v>
+      </c>
+      <c r="P13" t="s">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2111" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48DBA661-180D-4FE8-89CC-F54C65640100}"/>
+  <xr:revisionPtr revIDLastSave="2139" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC7BEFB0-1BC9-4371-A697-4B59346C432C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10503" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10521" uniqueCount="516">
   <si>
     <t>Year</t>
   </si>
@@ -1522,9 +1522,6 @@
     <t>Overturned</t>
   </si>
   <si>
-    <t>FP2</t>
-  </si>
-  <si>
     <t>Performed practice start outside designated practice area</t>
   </si>
   <si>
@@ -1568,6 +1565,15 @@
   </si>
   <si>
     <t>Cadillac</t>
+  </si>
+  <si>
+    <t>Performed practice start on the grid while another driver was stationary on the same side of the grid</t>
+  </si>
+  <si>
+    <t>Nish Shetty, Matthew Selley, Pedro Lamy, Zheng Honghai</t>
+  </si>
+  <si>
+    <t>Norris not on a push lap</t>
   </si>
 </sst>
 </file>
@@ -1652,6 +1658,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -45708,7 +45718,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -45784,7 +45794,7 @@
         <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>498</v>
+        <v>50</v>
       </c>
       <c r="G2" t="s">
         <v>125</v>
@@ -45793,10 +45803,10 @@
         <v>91</v>
       </c>
       <c r="O2" t="s">
+        <v>498</v>
+      </c>
+      <c r="P2" t="s">
         <v>499</v>
-      </c>
-      <c r="P2" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -45816,7 +45826,7 @@
         <v>38</v>
       </c>
       <c r="F3" t="s">
-        <v>498</v>
+        <v>50</v>
       </c>
       <c r="G3" t="s">
         <v>274</v>
@@ -45828,10 +45838,10 @@
         <v>84</v>
       </c>
       <c r="O3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="P3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
@@ -45851,7 +45861,7 @@
         <v>152</v>
       </c>
       <c r="F4" t="s">
-        <v>498</v>
+        <v>50</v>
       </c>
       <c r="G4" t="s">
         <v>278</v>
@@ -45863,10 +45873,10 @@
         <v>285</v>
       </c>
       <c r="O4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="P4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
@@ -45898,10 +45908,10 @@
         <v>7500</v>
       </c>
       <c r="O5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="P5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
@@ -45933,10 +45943,10 @@
         <v>5000</v>
       </c>
       <c r="O6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="P6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -45962,16 +45972,16 @@
         <v>274</v>
       </c>
       <c r="H7" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="J7" t="s">
         <v>285</v>
       </c>
       <c r="O7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="P7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
@@ -45988,22 +45998,22 @@
         <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F8" t="s">
         <v>222</v>
       </c>
       <c r="G8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="J8" t="s">
         <v>285</v>
       </c>
       <c r="O8" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="P8" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
@@ -46026,16 +46036,16 @@
         <v>222</v>
       </c>
       <c r="G9" t="s">
+        <v>509</v>
+      </c>
+      <c r="J9" t="s">
         <v>510</v>
       </c>
-      <c r="J9" t="s">
+      <c r="O9" t="s">
         <v>511</v>
       </c>
-      <c r="O9" t="s">
-        <v>512</v>
-      </c>
       <c r="P9" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
@@ -46070,7 +46080,7 @@
         <v>301</v>
       </c>
       <c r="P10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
@@ -46105,7 +46115,7 @@
         <v>301</v>
       </c>
       <c r="P11" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
@@ -46134,7 +46144,7 @@
         <v>285</v>
       </c>
       <c r="P12" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
@@ -46151,7 +46161,7 @@
         <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F13" t="s">
         <v>49</v>
@@ -46166,10 +46176,81 @@
         <v>285</v>
       </c>
       <c r="P13" t="s">
-        <v>500</v>
+        <v>499</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2026</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>216</v>
+      </c>
+      <c r="D14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" t="s">
+        <v>129</v>
+      </c>
+      <c r="I14" t="s">
+        <v>262</v>
+      </c>
+      <c r="J14" t="s">
+        <v>84</v>
+      </c>
+      <c r="O14" t="s">
+        <v>513</v>
+      </c>
+      <c r="P14" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>2026</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>216</v>
+      </c>
+      <c r="D15" t="s">
+        <v>262</v>
+      </c>
+      <c r="E15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" t="s">
+        <v>153</v>
+      </c>
+      <c r="G15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J15" t="s">
+        <v>285</v>
+      </c>
+      <c r="O15" t="s">
+        <v>515</v>
+      </c>
+      <c r="P15" t="s">
+        <v>514</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2139" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC7BEFB0-1BC9-4371-A697-4B59346C432C}"/>
+  <xr:revisionPtr revIDLastSave="2154" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D04F18B-2CA5-459A-BAAE-05B20E2FE5BC}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10521" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10530" uniqueCount="517">
   <si>
     <t>Year</t>
   </si>
@@ -1574,6 +1574,9 @@
   </si>
   <si>
     <t>Norris not on a push lap</t>
+  </si>
+  <si>
+    <t>Verstappen said he was not impeded</t>
   </si>
 </sst>
 </file>
@@ -45718,7 +45721,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -46249,6 +46252,41 @@
         <v>514</v>
       </c>
     </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2026</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>216</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" t="s">
+        <v>153</v>
+      </c>
+      <c r="G16" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" t="s">
+        <v>285</v>
+      </c>
+      <c r="O16" t="s">
+        <v>516</v>
+      </c>
+      <c r="P16" t="s">
+        <v>514</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2154" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D04F18B-2CA5-459A-BAAE-05B20E2FE5BC}"/>
+  <xr:revisionPtr revIDLastSave="2202" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10F42F54-033C-4D97-A892-AF87BEA1A9EC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10530" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10569" uniqueCount="519">
   <si>
     <t>Year</t>
   </si>
@@ -1577,6 +1577,12 @@
   </si>
   <si>
     <t>Verstappen said he was not impeded</t>
+  </si>
+  <si>
+    <t>Exceeding minimum time set by ECU behind SC</t>
+  </si>
+  <si>
+    <t>Isach Hadjar</t>
   </si>
 </sst>
 </file>
@@ -45721,7 +45727,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -46287,6 +46293,172 @@
         <v>514</v>
       </c>
     </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>2026</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>216</v>
+      </c>
+      <c r="D17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" t="s">
+        <v>153</v>
+      </c>
+      <c r="G17" t="s">
+        <v>271</v>
+      </c>
+      <c r="J17" t="s">
+        <v>11</v>
+      </c>
+      <c r="M17" t="s">
+        <v>245</v>
+      </c>
+      <c r="P17" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2026</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>216</v>
+      </c>
+      <c r="D18" t="s">
+        <v>262</v>
+      </c>
+      <c r="E18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" t="s">
+        <v>177</v>
+      </c>
+      <c r="G18" t="s">
+        <v>266</v>
+      </c>
+      <c r="I18" t="s">
+        <v>217</v>
+      </c>
+      <c r="J18" t="s">
+        <v>85</v>
+      </c>
+      <c r="K18">
+        <v>10</v>
+      </c>
+      <c r="P18" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>2026</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>216</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s">
+        <v>512</v>
+      </c>
+      <c r="F19" t="s">
+        <v>177</v>
+      </c>
+      <c r="G19" t="s">
+        <v>120</v>
+      </c>
+      <c r="J19" t="s">
+        <v>85</v>
+      </c>
+      <c r="K19">
+        <v>5</v>
+      </c>
+      <c r="O19" t="s">
+        <v>517</v>
+      </c>
+      <c r="P19" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>2026</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20" t="s">
+        <v>216</v>
+      </c>
+      <c r="D20" t="s">
+        <v>518</v>
+      </c>
+      <c r="E20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" t="s">
+        <v>177</v>
+      </c>
+      <c r="G20" t="s">
+        <v>125</v>
+      </c>
+      <c r="J20" t="s">
+        <v>91</v>
+      </c>
+      <c r="P20" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>2026</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>216</v>
+      </c>
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" t="s">
+        <v>152</v>
+      </c>
+      <c r="F21" t="s">
+        <v>222</v>
+      </c>
+      <c r="G21" t="s">
+        <v>236</v>
+      </c>
+      <c r="J21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21">
+        <v>5000</v>
+      </c>
+      <c r="O21" t="s">
+        <v>139</v>
+      </c>
+      <c r="P21" t="s">
+        <v>514</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2202" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10F42F54-033C-4D97-A892-AF87BEA1A9EC}"/>
+  <xr:revisionPtr revIDLastSave="2203" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{835FD78A-A8E5-496C-9336-4F30A4917340}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10569" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10569" uniqueCount="518">
   <si>
     <t>Year</t>
   </si>
@@ -1580,9 +1580,6 @@
   </si>
   <si>
     <t>Exceeding minimum time set by ECU behind SC</t>
-  </si>
-  <si>
-    <t>Isach Hadjar</t>
   </si>
 </sst>
 </file>
@@ -46406,7 +46403,7 @@
         <v>216</v>
       </c>
       <c r="D20" t="s">
-        <v>518</v>
+        <v>217</v>
       </c>
       <c r="E20" t="s">
         <v>40</v>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2203" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{835FD78A-A8E5-496C-9336-4F30A4917340}"/>
+  <xr:revisionPtr revIDLastSave="2221" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CCDFF87-94E6-4217-BF26-5AC80BEBEF29}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10569" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10585" uniqueCount="518">
   <si>
     <t>Year</t>
   </si>
@@ -45724,7 +45724,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -46456,6 +46456,73 @@
         <v>514</v>
       </c>
     </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>2026</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>216</v>
+      </c>
+      <c r="D22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" t="s">
+        <v>271</v>
+      </c>
+      <c r="J22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M22" t="s">
+        <v>245</v>
+      </c>
+      <c r="P22" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>2026</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>216</v>
+      </c>
+      <c r="D23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" t="s">
+        <v>49</v>
+      </c>
+      <c r="G23" t="s">
+        <v>266</v>
+      </c>
+      <c r="I23" t="s">
+        <v>218</v>
+      </c>
+      <c r="J23" t="s">
+        <v>85</v>
+      </c>
+      <c r="K23">
+        <v>10</v>
+      </c>
+      <c r="P23" t="s">
+        <v>514</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2221" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CCDFF87-94E6-4217-BF26-5AC80BEBEF29}"/>
+  <xr:revisionPtr revIDLastSave="2267" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92179759-0F4A-4339-9841-30DB0F480449}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10585" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10627" uniqueCount="521">
   <si>
     <t>Year</t>
   </si>
@@ -1580,6 +1580,15 @@
   </si>
   <si>
     <t>Exceeding minimum time set by ECU behind SC</t>
+  </si>
+  <si>
+    <t>Incident with Car 55</t>
+  </si>
+  <si>
+    <t>Gerd Ennser, Matthew Selley, Zhou Xiaoxu, Derek Warwick, Kazuhiro Tsuge</t>
+  </si>
+  <si>
+    <t>Neither driver to blame</t>
   </si>
 </sst>
 </file>
@@ -45724,7 +45733,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -46523,6 +46532,172 @@
         <v>514</v>
       </c>
     </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>2026</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>173</v>
+      </c>
+      <c r="D24" t="s">
+        <v>197</v>
+      </c>
+      <c r="E24" t="s">
+        <v>265</v>
+      </c>
+      <c r="F24" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" t="s">
+        <v>203</v>
+      </c>
+      <c r="H24" t="s">
+        <v>518</v>
+      </c>
+      <c r="I24" t="s">
+        <v>111</v>
+      </c>
+      <c r="J24" t="s">
+        <v>285</v>
+      </c>
+      <c r="P24" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>2026</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>173</v>
+      </c>
+      <c r="D25" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" t="s">
+        <v>266</v>
+      </c>
+      <c r="I25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" t="s">
+        <v>285</v>
+      </c>
+      <c r="O25" t="s">
+        <v>520</v>
+      </c>
+      <c r="P25" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>2026</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>173</v>
+      </c>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" t="s">
+        <v>56</v>
+      </c>
+      <c r="I26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J26" t="s">
+        <v>285</v>
+      </c>
+      <c r="P26" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>2026</v>
+      </c>
+      <c r="B27">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>173</v>
+      </c>
+      <c r="D27" t="s">
+        <v>218</v>
+      </c>
+      <c r="E27" t="s">
+        <v>152</v>
+      </c>
+      <c r="F27" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" t="s">
+        <v>56</v>
+      </c>
+      <c r="I27" t="s">
+        <v>26</v>
+      </c>
+      <c r="J27" t="s">
+        <v>91</v>
+      </c>
+      <c r="P27" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>2026</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>173</v>
+      </c>
+      <c r="D28" t="s">
+        <v>195</v>
+      </c>
+      <c r="E28" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28" t="s">
+        <v>56</v>
+      </c>
+      <c r="I28" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" t="s">
+        <v>91</v>
+      </c>
+      <c r="P28" t="s">
+        <v>519</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2267" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92179759-0F4A-4339-9841-30DB0F480449}"/>
+  <xr:revisionPtr revIDLastSave="2277" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3811D334-8C89-4F46-AEA3-C57C7C8732BD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10627" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10633" uniqueCount="522">
   <si>
     <t>Year</t>
   </si>
@@ -1589,6 +1589,9 @@
   </si>
   <si>
     <t>Neither driver to blame</t>
+  </si>
+  <si>
+    <t>Nish Shetty, Natalie Corsmit, Vitantonio Liuzzi, Steve Pence</t>
   </si>
 </sst>
 </file>
@@ -1673,10 +1676,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -45733,7 +45732,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -46698,6 +46697,35 @@
         <v>519</v>
       </c>
     </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>2026</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
+        <v>170</v>
+      </c>
+      <c r="D29" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" t="s">
+        <v>273</v>
+      </c>
+      <c r="L29">
+        <v>200</v>
+      </c>
+      <c r="P29" t="s">
+        <v>521</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2277" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3811D334-8C89-4F46-AEA3-C57C7C8732BD}"/>
+  <xr:revisionPtr revIDLastSave="2278" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A75146F-005B-4F8D-B5BE-0BAA0F58FA8E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10633" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10634" uniqueCount="522">
   <si>
     <t>Year</t>
   </si>
@@ -1676,6 +1676,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -46719,6 +46723,9 @@
       <c r="G29" t="s">
         <v>273</v>
       </c>
+      <c r="J29" t="s">
+        <v>10</v>
+      </c>
       <c r="L29">
         <v>200</v>
       </c>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2278" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A75146F-005B-4F8D-B5BE-0BAA0F58FA8E}"/>
+  <xr:revisionPtr revIDLastSave="2288" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C539E4A9-4B6B-49D9-9B2F-E11EFDABE943}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10634" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10642" uniqueCount="524">
   <si>
     <t>Year</t>
   </si>
@@ -1592,6 +1592,12 @@
   </si>
   <si>
     <t>Nish Shetty, Natalie Corsmit, Vitantonio Liuzzi, Steve Pence</t>
+  </si>
+  <si>
+    <t>Track Limits Violation</t>
+  </si>
+  <si>
+    <t>Driver exceeded track limits in SQ1 and should have been eliminated, but was erroneously permitted to continue to SQ2</t>
   </si>
 </sst>
 </file>
@@ -45736,7 +45742,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -46733,6 +46739,35 @@
         <v>521</v>
       </c>
     </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
+        <v>170</v>
+      </c>
+      <c r="D30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" t="s">
+        <v>153</v>
+      </c>
+      <c r="G30" t="s">
+        <v>522</v>
+      </c>
+      <c r="J30" t="s">
+        <v>11</v>
+      </c>
+      <c r="K30">
+        <v>5</v>
+      </c>
+      <c r="O30" t="s">
+        <v>523</v>
+      </c>
+      <c r="P30" t="s">
+        <v>521</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2288" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C539E4A9-4B6B-49D9-9B2F-E11EFDABE943}"/>
+  <xr:revisionPtr revIDLastSave="2296" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A6C41EC-C7AE-4386-9959-5200061F2AB3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10642" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10650" uniqueCount="525">
   <si>
     <t>Year</t>
   </si>
@@ -1598,6 +1598,9 @@
   </si>
   <si>
     <t>Driver exceeded track limits in SQ1 and should have been eliminated, but was erroneously permitted to continue to SQ2</t>
+  </si>
+  <si>
+    <t>Exceeded the 1:48.0 time limit between the Safety Car Lines</t>
   </si>
 </sst>
 </file>
@@ -45742,7 +45745,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -46768,6 +46771,32 @@
         <v>521</v>
       </c>
     </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C31" t="s">
+        <v>170</v>
+      </c>
+      <c r="D31" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" t="s">
+        <v>153</v>
+      </c>
+      <c r="G31" t="s">
+        <v>125</v>
+      </c>
+      <c r="J31" t="s">
+        <v>285</v>
+      </c>
+      <c r="O31" t="s">
+        <v>524</v>
+      </c>
+      <c r="P31" t="s">
+        <v>521</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2296" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A6C41EC-C7AE-4386-9959-5200061F2AB3}"/>
+  <xr:revisionPtr revIDLastSave="2300" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40E97FAD-7719-43F2-9CFD-A0EDCE7B558E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46743,6 +46743,12 @@
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>2026</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
       <c r="C30" t="s">
         <v>170</v>
       </c>
@@ -46772,6 +46778,12 @@
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>2026</v>
+      </c>
+      <c r="B31">
+        <v>4</v>
+      </c>
       <c r="C31" t="s">
         <v>170</v>
       </c>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2300" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40E97FAD-7719-43F2-9CFD-A0EDCE7B558E}"/>
+  <xr:revisionPtr revIDLastSave="2327" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{094DCA46-EF61-4C54-929A-326A69E0E6ED}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10650" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10675" uniqueCount="526">
   <si>
     <t>Year</t>
   </si>
@@ -1594,13 +1594,16 @@
     <t>Nish Shetty, Natalie Corsmit, Vitantonio Liuzzi, Steve Pence</t>
   </si>
   <si>
-    <t>Track Limits Violation</t>
-  </si>
-  <si>
     <t>Driver exceeded track limits in SQ1 and should have been eliminated, but was erroneously permitted to continue to SQ2</t>
   </si>
   <si>
     <t>Exceeded the 1:48.0 time limit between the Safety Car Lines</t>
+  </si>
+  <si>
+    <t>Team continued working on the car beyond covers-on time</t>
+  </si>
+  <si>
+    <t>Engine intake air pressure exceeded max. permitted limit</t>
   </si>
 </sst>
 </file>
@@ -45745,7 +45748,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -46762,7 +46765,7 @@
         <v>153</v>
       </c>
       <c r="G30" t="s">
-        <v>522</v>
+        <v>276</v>
       </c>
       <c r="J30" t="s">
         <v>11</v>
@@ -46771,7 +46774,7 @@
         <v>5</v>
       </c>
       <c r="O30" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="P30" t="s">
         <v>521</v>
@@ -46803,9 +46806,111 @@
         <v>285</v>
       </c>
       <c r="O31" t="s">
+        <v>523</v>
+      </c>
+      <c r="P31" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>2026</v>
+      </c>
+      <c r="B32">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>170</v>
+      </c>
+      <c r="D32" t="s">
+        <v>331</v>
+      </c>
+      <c r="E32" t="s">
+        <v>265</v>
+      </c>
+      <c r="F32" t="s">
+        <v>153</v>
+      </c>
+      <c r="G32" t="s">
+        <v>69</v>
+      </c>
+      <c r="J32" t="s">
+        <v>11</v>
+      </c>
+      <c r="M32" t="s">
+        <v>245</v>
+      </c>
+      <c r="O32" t="s">
         <v>524</v>
       </c>
-      <c r="P31" t="s">
+      <c r="P32" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>2026</v>
+      </c>
+      <c r="B33">
+        <v>4</v>
+      </c>
+      <c r="C33" t="s">
+        <v>170</v>
+      </c>
+      <c r="D33" t="s">
+        <v>262</v>
+      </c>
+      <c r="E33" t="s">
+        <v>38</v>
+      </c>
+      <c r="F33" t="s">
+        <v>177</v>
+      </c>
+      <c r="G33" t="s">
+        <v>127</v>
+      </c>
+      <c r="J33" t="s">
+        <v>85</v>
+      </c>
+      <c r="K33">
+        <v>5</v>
+      </c>
+      <c r="P33" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>2026</v>
+      </c>
+      <c r="B34">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
+        <v>170</v>
+      </c>
+      <c r="D34" t="s">
+        <v>263</v>
+      </c>
+      <c r="E34" t="s">
+        <v>506</v>
+      </c>
+      <c r="F34" t="s">
+        <v>177</v>
+      </c>
+      <c r="G34" t="s">
+        <v>122</v>
+      </c>
+      <c r="H34" t="s">
+        <v>525</v>
+      </c>
+      <c r="J34" t="s">
+        <v>87</v>
+      </c>
+      <c r="O34" t="s">
+        <v>525</v>
+      </c>
+      <c r="P34" t="s">
         <v>521</v>
       </c>
     </row>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2327" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{094DCA46-EF61-4C54-929A-326A69E0E6ED}"/>
+  <xr:revisionPtr revIDLastSave="2338" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC3E6203-8AFC-4EF2-809E-606678E79EB8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10675" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10684" uniqueCount="528">
   <si>
     <t>Year</t>
   </si>
@@ -1604,6 +1604,12 @@
   </si>
   <si>
     <t>Engine intake air pressure exceeded max. permitted limit</t>
+  </si>
+  <si>
+    <t>The lhs and rhs floor board were protruding 2mm out of the reference volume RV-FLOOR BOARD</t>
+  </si>
+  <si>
+    <t>The lhs and rhs floor board were protruding 2mm out of the reference volume RV-FLOOR BOARD.</t>
   </si>
 </sst>
 </file>
@@ -45748,7 +45754,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -46914,6 +46920,41 @@
         <v>521</v>
       </c>
     </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>2026</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>170</v>
+      </c>
+      <c r="D35" t="s">
+        <v>217</v>
+      </c>
+      <c r="E35" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" t="s">
+        <v>48</v>
+      </c>
+      <c r="G35" t="s">
+        <v>122</v>
+      </c>
+      <c r="H35" t="s">
+        <v>526</v>
+      </c>
+      <c r="J35" t="s">
+        <v>87</v>
+      </c>
+      <c r="O35" t="s">
+        <v>527</v>
+      </c>
+      <c r="P35" t="s">
+        <v>521</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2338" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC3E6203-8AFC-4EF2-809E-606678E79EB8}"/>
+  <xr:revisionPtr revIDLastSave="2398" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE9617D3-6042-4276-8720-A7B137E777BE}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10684" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10756" uniqueCount="533">
   <si>
     <t>Year</t>
   </si>
@@ -1610,6 +1610,21 @@
   </si>
   <si>
     <t>The lhs and rhs floor board were protruding 2mm out of the reference volume RV-FLOOR BOARD.</t>
+  </si>
+  <si>
+    <t>Both drivers considered it to be a minor racing incident</t>
+  </si>
+  <si>
+    <t>Leaving the track on several occasions w/o justifiable reason</t>
+  </si>
+  <si>
+    <t>Drive Through Penalty imposed after the race and converted to 20 second time penalty</t>
+  </si>
+  <si>
+    <t>Crossing the white line at pit exit</t>
+  </si>
+  <si>
+    <t>Gear box failure caused driver to lose control of the car</t>
   </si>
 </sst>
 </file>
@@ -45754,7 +45769,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -46955,6 +46970,300 @@
         <v>521</v>
       </c>
     </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>2026</v>
+      </c>
+      <c r="B36">
+        <v>4</v>
+      </c>
+      <c r="C36" t="s">
+        <v>170</v>
+      </c>
+      <c r="D36" t="s">
+        <v>466</v>
+      </c>
+      <c r="E36" t="s">
+        <v>512</v>
+      </c>
+      <c r="F36" t="s">
+        <v>49</v>
+      </c>
+      <c r="G36" t="s">
+        <v>273</v>
+      </c>
+      <c r="J36" t="s">
+        <v>334</v>
+      </c>
+      <c r="P36" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>2026</v>
+      </c>
+      <c r="B37">
+        <v>4</v>
+      </c>
+      <c r="C37" t="s">
+        <v>170</v>
+      </c>
+      <c r="D37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F37" t="s">
+        <v>49</v>
+      </c>
+      <c r="G37" t="s">
+        <v>114</v>
+      </c>
+      <c r="J37" t="s">
+        <v>285</v>
+      </c>
+      <c r="P37" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>2026</v>
+      </c>
+      <c r="B38">
+        <v>4</v>
+      </c>
+      <c r="C38" t="s">
+        <v>170</v>
+      </c>
+      <c r="D38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" t="s">
+        <v>45</v>
+      </c>
+      <c r="F38" t="s">
+        <v>49</v>
+      </c>
+      <c r="G38" t="s">
+        <v>114</v>
+      </c>
+      <c r="J38" t="s">
+        <v>285</v>
+      </c>
+      <c r="P38" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>2026</v>
+      </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>170</v>
+      </c>
+      <c r="D39" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" t="s">
+        <v>150</v>
+      </c>
+      <c r="F39" t="s">
+        <v>49</v>
+      </c>
+      <c r="G39" t="s">
+        <v>114</v>
+      </c>
+      <c r="J39" t="s">
+        <v>285</v>
+      </c>
+      <c r="P39" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>2026</v>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>170</v>
+      </c>
+      <c r="D40" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40" t="s">
+        <v>49</v>
+      </c>
+      <c r="G40" t="s">
+        <v>266</v>
+      </c>
+      <c r="I40" t="s">
+        <v>37</v>
+      </c>
+      <c r="J40" t="s">
+        <v>285</v>
+      </c>
+      <c r="O40" t="s">
+        <v>528</v>
+      </c>
+      <c r="P40" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>2026</v>
+      </c>
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>170</v>
+      </c>
+      <c r="D41" t="s">
+        <v>37</v>
+      </c>
+      <c r="E41" t="s">
+        <v>38</v>
+      </c>
+      <c r="F41" t="s">
+        <v>49</v>
+      </c>
+      <c r="G41" t="s">
+        <v>266</v>
+      </c>
+      <c r="I41" t="s">
+        <v>26</v>
+      </c>
+      <c r="J41" t="s">
+        <v>285</v>
+      </c>
+      <c r="O41" t="s">
+        <v>528</v>
+      </c>
+      <c r="P41" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>2026</v>
+      </c>
+      <c r="B42">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>170</v>
+      </c>
+      <c r="D42" t="s">
+        <v>29</v>
+      </c>
+      <c r="E42" t="s">
+        <v>41</v>
+      </c>
+      <c r="F42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G42" t="s">
+        <v>127</v>
+      </c>
+      <c r="H42" t="s">
+        <v>529</v>
+      </c>
+      <c r="J42" t="s">
+        <v>85</v>
+      </c>
+      <c r="K42">
+        <v>20</v>
+      </c>
+      <c r="O42" t="s">
+        <v>530</v>
+      </c>
+      <c r="P42" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>2026</v>
+      </c>
+      <c r="B43">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>170</v>
+      </c>
+      <c r="D43" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" t="s">
+        <v>40</v>
+      </c>
+      <c r="F43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G43" t="s">
+        <v>123</v>
+      </c>
+      <c r="H43" t="s">
+        <v>531</v>
+      </c>
+      <c r="J43" t="s">
+        <v>85</v>
+      </c>
+      <c r="K43">
+        <v>5</v>
+      </c>
+      <c r="P43" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>2026</v>
+      </c>
+      <c r="B44">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
+        <v>170</v>
+      </c>
+      <c r="D44" t="s">
+        <v>197</v>
+      </c>
+      <c r="E44" t="s">
+        <v>265</v>
+      </c>
+      <c r="F44" t="s">
+        <v>49</v>
+      </c>
+      <c r="G44" t="s">
+        <v>266</v>
+      </c>
+      <c r="I44" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" t="s">
+        <v>285</v>
+      </c>
+      <c r="O44" t="s">
+        <v>532</v>
+      </c>
+      <c r="P44" t="s">
+        <v>521</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2459" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7471DEC-47A0-46AF-917B-D38C6EF3FCAC}"/>
+  <xr:revisionPtr revIDLastSave="2560" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F742792A-5264-47E1-8B8A-19A712C44060}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10796" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10910" uniqueCount="544">
   <si>
     <t>Year</t>
   </si>
@@ -1640,6 +1640,24 @@
   </si>
   <si>
     <t>Exceeded time limit between the safety car lines</t>
+  </si>
+  <si>
+    <t>Failure to start formation lap</t>
+  </si>
+  <si>
+    <t>Procedural Infringement</t>
+  </si>
+  <si>
+    <t>Reported as having air released on the left rear tire with the wheel fitted to the car</t>
+  </si>
+  <si>
+    <t>Released into path of another car</t>
+  </si>
+  <si>
+    <t>Released from garage with wheel covers still fitted</t>
+  </si>
+  <si>
+    <t>Driver's first reprimand of the season</t>
   </si>
 </sst>
 </file>
@@ -45784,7 +45802,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -47445,6 +47463,472 @@
         <v>533</v>
       </c>
     </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>2026</v>
+      </c>
+      <c r="B50">
+        <v>5</v>
+      </c>
+      <c r="C50" t="s">
+        <v>168</v>
+      </c>
+      <c r="D50" t="s">
+        <v>463</v>
+      </c>
+      <c r="E50" t="s">
+        <v>509</v>
+      </c>
+      <c r="F50" t="s">
+        <v>150</v>
+      </c>
+      <c r="G50" t="s">
+        <v>268</v>
+      </c>
+      <c r="J50" t="s">
+        <v>11</v>
+      </c>
+      <c r="M50" t="s">
+        <v>242</v>
+      </c>
+      <c r="P50" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>2026</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>168</v>
+      </c>
+      <c r="D51" t="s">
+        <v>217</v>
+      </c>
+      <c r="E51" t="s">
+        <v>39</v>
+      </c>
+      <c r="F51" t="s">
+        <v>150</v>
+      </c>
+      <c r="G51" t="s">
+        <v>268</v>
+      </c>
+      <c r="J51" t="s">
+        <v>11</v>
+      </c>
+      <c r="M51" t="s">
+        <v>242</v>
+      </c>
+      <c r="P51" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>2026</v>
+      </c>
+      <c r="B52">
+        <v>5</v>
+      </c>
+      <c r="C52" t="s">
+        <v>168</v>
+      </c>
+      <c r="D52" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" t="s">
+        <v>149</v>
+      </c>
+      <c r="F52" t="s">
+        <v>150</v>
+      </c>
+      <c r="G52" t="s">
+        <v>268</v>
+      </c>
+      <c r="J52" t="s">
+        <v>11</v>
+      </c>
+      <c r="M52" t="s">
+        <v>242</v>
+      </c>
+      <c r="P52" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>2026</v>
+      </c>
+      <c r="B53">
+        <v>5</v>
+      </c>
+      <c r="C53" t="s">
+        <v>168</v>
+      </c>
+      <c r="D53" t="s">
+        <v>36</v>
+      </c>
+      <c r="E53" t="s">
+        <v>45</v>
+      </c>
+      <c r="F53" t="s">
+        <v>150</v>
+      </c>
+      <c r="G53" t="s">
+        <v>268</v>
+      </c>
+      <c r="J53" t="s">
+        <v>11</v>
+      </c>
+      <c r="M53" t="s">
+        <v>242</v>
+      </c>
+      <c r="P53" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>2026</v>
+      </c>
+      <c r="B54">
+        <v>5</v>
+      </c>
+      <c r="C54" t="s">
+        <v>168</v>
+      </c>
+      <c r="D54" t="s">
+        <v>28</v>
+      </c>
+      <c r="E54" t="s">
+        <v>147</v>
+      </c>
+      <c r="F54" t="s">
+        <v>174</v>
+      </c>
+      <c r="G54" t="s">
+        <v>504</v>
+      </c>
+      <c r="J54" t="s">
+        <v>282</v>
+      </c>
+      <c r="O54" t="s">
+        <v>538</v>
+      </c>
+      <c r="P54" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>2026</v>
+      </c>
+      <c r="B55">
+        <v>5</v>
+      </c>
+      <c r="C55" t="s">
+        <v>168</v>
+      </c>
+      <c r="D55" t="s">
+        <v>27</v>
+      </c>
+      <c r="E55" t="s">
+        <v>503</v>
+      </c>
+      <c r="F55" t="s">
+        <v>174</v>
+      </c>
+      <c r="G55" t="s">
+        <v>335</v>
+      </c>
+      <c r="I55" t="s">
+        <v>194</v>
+      </c>
+      <c r="J55" t="s">
+        <v>82</v>
+      </c>
+      <c r="K55">
+        <v>10</v>
+      </c>
+      <c r="P55" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>2026</v>
+      </c>
+      <c r="B56">
+        <v>5</v>
+      </c>
+      <c r="C56" t="s">
+        <v>168</v>
+      </c>
+      <c r="D56" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" t="s">
+        <v>509</v>
+      </c>
+      <c r="F56" t="s">
+        <v>174</v>
+      </c>
+      <c r="G56" t="s">
+        <v>65</v>
+      </c>
+      <c r="I56" t="s">
+        <v>194</v>
+      </c>
+      <c r="J56" t="s">
+        <v>82</v>
+      </c>
+      <c r="K56">
+        <v>10</v>
+      </c>
+      <c r="P56" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>2026</v>
+      </c>
+      <c r="B57">
+        <v>5</v>
+      </c>
+      <c r="C57" t="s">
+        <v>168</v>
+      </c>
+      <c r="D57" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" t="s">
+        <v>41</v>
+      </c>
+      <c r="F57" t="s">
+        <v>174</v>
+      </c>
+      <c r="G57" t="s">
+        <v>335</v>
+      </c>
+      <c r="I57" t="s">
+        <v>192</v>
+      </c>
+      <c r="J57" t="s">
+        <v>282</v>
+      </c>
+      <c r="P57" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>2026</v>
+      </c>
+      <c r="B58">
+        <v>5</v>
+      </c>
+      <c r="C58" t="s">
+        <v>168</v>
+      </c>
+      <c r="D58" t="s">
+        <v>30</v>
+      </c>
+      <c r="E58" t="s">
+        <v>39</v>
+      </c>
+      <c r="F58" t="s">
+        <v>174</v>
+      </c>
+      <c r="G58" t="s">
+        <v>119</v>
+      </c>
+      <c r="H58" t="s">
+        <v>539</v>
+      </c>
+      <c r="J58" t="s">
+        <v>282</v>
+      </c>
+      <c r="O58" t="s">
+        <v>540</v>
+      </c>
+      <c r="P58" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>2026</v>
+      </c>
+      <c r="B59">
+        <v>5</v>
+      </c>
+      <c r="C59" t="s">
+        <v>168</v>
+      </c>
+      <c r="D59" t="s">
+        <v>32</v>
+      </c>
+      <c r="E59" t="s">
+        <v>147</v>
+      </c>
+      <c r="F59" t="s">
+        <v>48</v>
+      </c>
+      <c r="G59" t="s">
+        <v>233</v>
+      </c>
+      <c r="I59" t="s">
+        <v>215</v>
+      </c>
+      <c r="J59" t="s">
+        <v>10</v>
+      </c>
+      <c r="L59">
+        <v>5000</v>
+      </c>
+      <c r="O59" t="s">
+        <v>541</v>
+      </c>
+      <c r="P59" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>2026</v>
+      </c>
+      <c r="B60">
+        <v>5</v>
+      </c>
+      <c r="C60" t="s">
+        <v>168</v>
+      </c>
+      <c r="D60" t="s">
+        <v>28</v>
+      </c>
+      <c r="E60" t="s">
+        <v>147</v>
+      </c>
+      <c r="F60" t="s">
+        <v>48</v>
+      </c>
+      <c r="G60" t="s">
+        <v>233</v>
+      </c>
+      <c r="J60" t="s">
+        <v>10</v>
+      </c>
+      <c r="L60">
+        <v>7000</v>
+      </c>
+      <c r="O60" t="s">
+        <v>542</v>
+      </c>
+      <c r="P60" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>2026</v>
+      </c>
+      <c r="B61">
+        <v>5</v>
+      </c>
+      <c r="C61" t="s">
+        <v>168</v>
+      </c>
+      <c r="D61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61" t="s">
+        <v>509</v>
+      </c>
+      <c r="F61" t="s">
+        <v>48</v>
+      </c>
+      <c r="G61" t="s">
+        <v>122</v>
+      </c>
+      <c r="J61" t="s">
+        <v>81</v>
+      </c>
+      <c r="O61" t="s">
+        <v>543</v>
+      </c>
+      <c r="P61" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>2026</v>
+      </c>
+      <c r="B62">
+        <v>5</v>
+      </c>
+      <c r="C62" t="s">
+        <v>168</v>
+      </c>
+      <c r="D62" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" t="s">
+        <v>41</v>
+      </c>
+      <c r="F62" t="s">
+        <v>48</v>
+      </c>
+      <c r="G62" t="s">
+        <v>53</v>
+      </c>
+      <c r="I62" t="s">
+        <v>25</v>
+      </c>
+      <c r="J62" t="s">
+        <v>282</v>
+      </c>
+      <c r="P62" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>2026</v>
+      </c>
+      <c r="B63">
+        <v>5</v>
+      </c>
+      <c r="C63" t="s">
+        <v>168</v>
+      </c>
+      <c r="D63" t="s">
+        <v>28</v>
+      </c>
+      <c r="E63" t="s">
+        <v>147</v>
+      </c>
+      <c r="F63" t="s">
+        <v>48</v>
+      </c>
+      <c r="G63" t="s">
+        <v>53</v>
+      </c>
+      <c r="I63" t="s">
+        <v>27</v>
+      </c>
+      <c r="J63" t="s">
+        <v>282</v>
+      </c>
+      <c r="P63" t="s">
+        <v>533</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2560" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F742792A-5264-47E1-8B8A-19A712C44060}"/>
+  <xr:revisionPtr revIDLastSave="2639" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0A13ABC-AB29-4AAE-BD4A-FF43F610198C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10910" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10987" uniqueCount="548">
   <si>
     <t>Year</t>
   </si>
@@ -1658,6 +1658,18 @@
   </si>
   <si>
     <t>Driver's first reprimand of the season</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exceeded the VSC delta </t>
+  </si>
+  <si>
+    <t>Suspended through end of season</t>
+  </si>
+  <si>
+    <t>Unsafe Act</t>
+  </si>
+  <si>
+    <t>Threw head restraint onto the track. Fine suspended for 12 month period</t>
   </si>
 </sst>
 </file>
@@ -45802,13 +45814,16 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P63"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
     <col min="8" max="8" width="31" customWidth="1"/>
     <col min="9" max="9" width="22.6640625" customWidth="1"/>
     <col min="11" max="11" width="22.21875" customWidth="1"/>
+    <col min="13" max="13" width="12.21875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="15" width="26.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -47929,6 +47944,332 @@
         <v>533</v>
       </c>
     </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>2026</v>
+      </c>
+      <c r="B64">
+        <v>5</v>
+      </c>
+      <c r="C64" t="s">
+        <v>168</v>
+      </c>
+      <c r="D64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E64" t="s">
+        <v>147</v>
+      </c>
+      <c r="F64" t="s">
+        <v>49</v>
+      </c>
+      <c r="G64" t="s">
+        <v>113</v>
+      </c>
+      <c r="J64" t="s">
+        <v>11</v>
+      </c>
+      <c r="M64" t="s">
+        <v>242</v>
+      </c>
+      <c r="P64" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>2026</v>
+      </c>
+      <c r="B65">
+        <v>5</v>
+      </c>
+      <c r="C65" t="s">
+        <v>168</v>
+      </c>
+      <c r="D65" t="s">
+        <v>27</v>
+      </c>
+      <c r="E65" t="s">
+        <v>503</v>
+      </c>
+      <c r="F65" t="s">
+        <v>49</v>
+      </c>
+      <c r="G65" t="s">
+        <v>270</v>
+      </c>
+      <c r="J65" t="s">
+        <v>82</v>
+      </c>
+      <c r="K65">
+        <v>5</v>
+      </c>
+      <c r="P65" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>2026</v>
+      </c>
+      <c r="B66">
+        <v>5</v>
+      </c>
+      <c r="C66" t="s">
+        <v>168</v>
+      </c>
+      <c r="D66" t="s">
+        <v>463</v>
+      </c>
+      <c r="E66" t="s">
+        <v>509</v>
+      </c>
+      <c r="F66" t="s">
+        <v>49</v>
+      </c>
+      <c r="G66" t="s">
+        <v>270</v>
+      </c>
+      <c r="J66" t="s">
+        <v>82</v>
+      </c>
+      <c r="K66">
+        <v>5</v>
+      </c>
+      <c r="P66" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>2026</v>
+      </c>
+      <c r="B67">
+        <v>5</v>
+      </c>
+      <c r="C67" t="s">
+        <v>168</v>
+      </c>
+      <c r="D67" t="s">
+        <v>260</v>
+      </c>
+      <c r="E67" t="s">
+        <v>503</v>
+      </c>
+      <c r="F67" t="s">
+        <v>49</v>
+      </c>
+      <c r="G67" t="s">
+        <v>275</v>
+      </c>
+      <c r="J67" t="s">
+        <v>82</v>
+      </c>
+      <c r="K67">
+        <v>5</v>
+      </c>
+      <c r="O67" t="s">
+        <v>544</v>
+      </c>
+      <c r="P67" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>2026</v>
+      </c>
+      <c r="B68">
+        <v>5</v>
+      </c>
+      <c r="C68" t="s">
+        <v>168</v>
+      </c>
+      <c r="D68" t="s">
+        <v>27</v>
+      </c>
+      <c r="E68" t="s">
+        <v>503</v>
+      </c>
+      <c r="F68" t="s">
+        <v>49</v>
+      </c>
+      <c r="G68" t="s">
+        <v>504</v>
+      </c>
+      <c r="J68" t="s">
+        <v>507</v>
+      </c>
+      <c r="O68" t="s">
+        <v>545</v>
+      </c>
+      <c r="P68" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>2026</v>
+      </c>
+      <c r="B69">
+        <v>5</v>
+      </c>
+      <c r="C69" t="s">
+        <v>168</v>
+      </c>
+      <c r="D69" t="s">
+        <v>192</v>
+      </c>
+      <c r="E69" t="s">
+        <v>42</v>
+      </c>
+      <c r="F69" t="s">
+        <v>49</v>
+      </c>
+      <c r="G69" t="s">
+        <v>263</v>
+      </c>
+      <c r="I69" t="s">
+        <v>36</v>
+      </c>
+      <c r="J69" t="s">
+        <v>82</v>
+      </c>
+      <c r="K69">
+        <v>10</v>
+      </c>
+      <c r="P69" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>2026</v>
+      </c>
+      <c r="B70">
+        <v>5</v>
+      </c>
+      <c r="C70" t="s">
+        <v>168</v>
+      </c>
+      <c r="D70" t="s">
+        <v>23</v>
+      </c>
+      <c r="E70" t="s">
+        <v>509</v>
+      </c>
+      <c r="F70" t="s">
+        <v>49</v>
+      </c>
+      <c r="G70" t="s">
+        <v>313</v>
+      </c>
+      <c r="J70" t="s">
+        <v>282</v>
+      </c>
+      <c r="P70" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>2026</v>
+      </c>
+      <c r="B71">
+        <v>5</v>
+      </c>
+      <c r="C71" t="s">
+        <v>168</v>
+      </c>
+      <c r="D71" t="s">
+        <v>194</v>
+      </c>
+      <c r="E71" t="s">
+        <v>262</v>
+      </c>
+      <c r="F71" t="s">
+        <v>49</v>
+      </c>
+      <c r="G71" t="s">
+        <v>504</v>
+      </c>
+      <c r="I71" t="s">
+        <v>27</v>
+      </c>
+      <c r="J71" t="s">
+        <v>81</v>
+      </c>
+      <c r="O71" t="s">
+        <v>543</v>
+      </c>
+      <c r="P71" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>2026</v>
+      </c>
+      <c r="B72">
+        <v>5</v>
+      </c>
+      <c r="C72" t="s">
+        <v>168</v>
+      </c>
+      <c r="D72" t="s">
+        <v>37</v>
+      </c>
+      <c r="E72" t="s">
+        <v>38</v>
+      </c>
+      <c r="F72" t="s">
+        <v>49</v>
+      </c>
+      <c r="G72" t="s">
+        <v>546</v>
+      </c>
+      <c r="J72" t="s">
+        <v>10</v>
+      </c>
+      <c r="L72">
+        <v>5000</v>
+      </c>
+      <c r="O72" t="s">
+        <v>547</v>
+      </c>
+      <c r="P72" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>2026</v>
+      </c>
+      <c r="B73">
+        <v>5</v>
+      </c>
+      <c r="C73" t="s">
+        <v>168</v>
+      </c>
+      <c r="D73" t="s">
+        <v>214</v>
+      </c>
+      <c r="E73" t="s">
+        <v>40</v>
+      </c>
+      <c r="F73" t="s">
+        <v>49</v>
+      </c>
+      <c r="G73" t="s">
+        <v>111</v>
+      </c>
+      <c r="J73" t="s">
+        <v>316</v>
+      </c>
+      <c r="P73" t="s">
+        <v>533</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2639" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0A13ABC-AB29-4AAE-BD4A-FF43F610198C}"/>
+  <xr:revisionPtr revIDLastSave="2707" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3110097F-C7E8-4C35-AE8B-E508E680DD99}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10987" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11049" uniqueCount="551">
   <si>
     <t>Year</t>
   </si>
@@ -1670,6 +1670,15 @@
   </si>
   <si>
     <t>Threw head restraint onto the track. Fine suspended for 12 month period</t>
+  </si>
+  <si>
+    <t>Driver was late to attend Thursday press conference</t>
+  </si>
+  <si>
+    <t>Fine suspended for period of 12 months</t>
+  </si>
+  <si>
+    <t>Garry Connelly, Derek Warwick, Tanja Geilhausen, Jean-Francois Calmes</t>
   </si>
 </sst>
 </file>
@@ -45814,7 +45823,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P73"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -48270,6 +48279,271 @@
         <v>533</v>
       </c>
     </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>2026</v>
+      </c>
+      <c r="B74">
+        <v>6</v>
+      </c>
+      <c r="C74" t="s">
+        <v>138</v>
+      </c>
+      <c r="D74" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" t="s">
+        <v>42</v>
+      </c>
+      <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
+        <v>199</v>
+      </c>
+      <c r="H74" t="s">
+        <v>548</v>
+      </c>
+      <c r="J74" t="s">
+        <v>10</v>
+      </c>
+      <c r="L74">
+        <v>5000</v>
+      </c>
+      <c r="O74" t="s">
+        <v>549</v>
+      </c>
+      <c r="P74" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>2026</v>
+      </c>
+      <c r="B75">
+        <v>6</v>
+      </c>
+      <c r="C75" t="s">
+        <v>138</v>
+      </c>
+      <c r="D75" t="s">
+        <v>29</v>
+      </c>
+      <c r="E75" t="s">
+        <v>41</v>
+      </c>
+      <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
+        <v>199</v>
+      </c>
+      <c r="H75" t="s">
+        <v>548</v>
+      </c>
+      <c r="J75" t="s">
+        <v>10</v>
+      </c>
+      <c r="L75">
+        <v>5000</v>
+      </c>
+      <c r="O75" t="s">
+        <v>549</v>
+      </c>
+      <c r="P75" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>2026</v>
+      </c>
+      <c r="B76">
+        <v>6</v>
+      </c>
+      <c r="C76" t="s">
+        <v>138</v>
+      </c>
+      <c r="D76" t="s">
+        <v>37</v>
+      </c>
+      <c r="E76" t="s">
+        <v>38</v>
+      </c>
+      <c r="F76" t="s">
+        <v>530</v>
+      </c>
+      <c r="G76" t="s">
+        <v>270</v>
+      </c>
+      <c r="J76" t="s">
+        <v>10</v>
+      </c>
+      <c r="L76">
+        <v>100</v>
+      </c>
+      <c r="P76" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>2026</v>
+      </c>
+      <c r="B77">
+        <v>6</v>
+      </c>
+      <c r="C77" t="s">
+        <v>138</v>
+      </c>
+      <c r="D77" t="s">
+        <v>29</v>
+      </c>
+      <c r="E77" t="s">
+        <v>41</v>
+      </c>
+      <c r="F77" t="s">
+        <v>530</v>
+      </c>
+      <c r="G77" t="s">
+        <v>53</v>
+      </c>
+      <c r="I77" t="s">
+        <v>194</v>
+      </c>
+      <c r="J77" t="s">
+        <v>88</v>
+      </c>
+      <c r="P77" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>2026</v>
+      </c>
+      <c r="B78">
+        <v>6</v>
+      </c>
+      <c r="C78" t="s">
+        <v>138</v>
+      </c>
+      <c r="D78" t="s">
+        <v>328</v>
+      </c>
+      <c r="E78" t="s">
+        <v>262</v>
+      </c>
+      <c r="F78" t="s">
+        <v>530</v>
+      </c>
+      <c r="G78" t="s">
+        <v>53</v>
+      </c>
+      <c r="I78" t="s">
+        <v>192</v>
+      </c>
+      <c r="J78" t="s">
+        <v>88</v>
+      </c>
+      <c r="P78" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>2026</v>
+      </c>
+      <c r="B79">
+        <v>6</v>
+      </c>
+      <c r="C79" t="s">
+        <v>138</v>
+      </c>
+      <c r="D79" t="s">
+        <v>194</v>
+      </c>
+      <c r="E79" t="s">
+        <v>262</v>
+      </c>
+      <c r="F79" t="s">
+        <v>530</v>
+      </c>
+      <c r="G79" t="s">
+        <v>120</v>
+      </c>
+      <c r="J79" t="s">
+        <v>282</v>
+      </c>
+      <c r="P79" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>2026</v>
+      </c>
+      <c r="B80">
+        <v>6</v>
+      </c>
+      <c r="C80" t="s">
+        <v>138</v>
+      </c>
+      <c r="D80" t="s">
+        <v>32</v>
+      </c>
+      <c r="E80" t="s">
+        <v>147</v>
+      </c>
+      <c r="F80" t="s">
+        <v>531</v>
+      </c>
+      <c r="G80" t="s">
+        <v>270</v>
+      </c>
+      <c r="J80" t="s">
+        <v>10</v>
+      </c>
+      <c r="L80">
+        <v>100</v>
+      </c>
+      <c r="P80" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>2026</v>
+      </c>
+      <c r="B81">
+        <v>6</v>
+      </c>
+      <c r="C81" t="s">
+        <v>138</v>
+      </c>
+      <c r="D81" t="s">
+        <v>259</v>
+      </c>
+      <c r="E81" t="s">
+        <v>38</v>
+      </c>
+      <c r="F81" t="s">
+        <v>531</v>
+      </c>
+      <c r="G81" t="s">
+        <v>270</v>
+      </c>
+      <c r="J81" t="s">
+        <v>10</v>
+      </c>
+      <c r="L81">
+        <v>100</v>
+      </c>
+      <c r="P81" t="s">
+        <v>550</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2707" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3110097F-C7E8-4C35-AE8B-E508E680DD99}"/>
+  <xr:revisionPtr revIDLastSave="2739" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27EDF473-4C5C-4DB4-A063-2AC536DBAB97}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11049" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11072" uniqueCount="552">
   <si>
     <t>Year</t>
   </si>
@@ -1679,6 +1679,9 @@
   </si>
   <si>
     <t>Garry Connelly, Derek Warwick, Tanja Geilhausen, Jean-Francois Calmes</t>
+  </si>
+  <si>
+    <t>10,000 of fine suspended for period of 12 months subject to no further breach of this regulation</t>
   </si>
 </sst>
 </file>
@@ -45823,7 +45826,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P81"/>
+  <dimension ref="A1:P84"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -48544,6 +48547,108 @@
         <v>550</v>
       </c>
     </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>2026</v>
+      </c>
+      <c r="B82">
+        <v>6</v>
+      </c>
+      <c r="C82" t="s">
+        <v>138</v>
+      </c>
+      <c r="D82" t="s">
+        <v>35</v>
+      </c>
+      <c r="E82" t="s">
+        <v>42</v>
+      </c>
+      <c r="F82" t="s">
+        <v>531</v>
+      </c>
+      <c r="G82" t="s">
+        <v>119</v>
+      </c>
+      <c r="H82" t="s">
+        <v>535</v>
+      </c>
+      <c r="J82" t="s">
+        <v>10</v>
+      </c>
+      <c r="L82">
+        <v>30000</v>
+      </c>
+      <c r="O82" t="s">
+        <v>551</v>
+      </c>
+      <c r="P82" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>2026</v>
+      </c>
+      <c r="B83">
+        <v>6</v>
+      </c>
+      <c r="C83" t="s">
+        <v>138</v>
+      </c>
+      <c r="D83" t="s">
+        <v>215</v>
+      </c>
+      <c r="E83" t="s">
+        <v>149</v>
+      </c>
+      <c r="F83" t="s">
+        <v>532</v>
+      </c>
+      <c r="G83" t="s">
+        <v>270</v>
+      </c>
+      <c r="J83" t="s">
+        <v>10</v>
+      </c>
+      <c r="L83">
+        <v>900</v>
+      </c>
+      <c r="P83" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>2026</v>
+      </c>
+      <c r="B84">
+        <v>6</v>
+      </c>
+      <c r="C84" t="s">
+        <v>138</v>
+      </c>
+      <c r="D84" t="s">
+        <v>36</v>
+      </c>
+      <c r="E84" t="s">
+        <v>45</v>
+      </c>
+      <c r="F84" t="s">
+        <v>532</v>
+      </c>
+      <c r="G84" t="s">
+        <v>270</v>
+      </c>
+      <c r="J84" t="s">
+        <v>10</v>
+      </c>
+      <c r="L84">
+        <v>100</v>
+      </c>
+      <c r="P84" t="s">
+        <v>550</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2739" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27EDF473-4C5C-4DB4-A063-2AC536DBAB97}"/>
+  <xr:revisionPtr revIDLastSave="2761" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7D1B7AD-5A3F-4E9D-8160-BC68DCB9DC10}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11072" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11088" uniqueCount="552">
   <si>
     <t>Year</t>
   </si>
@@ -45826,7 +45826,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P84"/>
+  <dimension ref="A1:P86"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -48649,6 +48649,73 @@
         <v>550</v>
       </c>
     </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>2026</v>
+      </c>
+      <c r="B85">
+        <v>6</v>
+      </c>
+      <c r="C85" t="s">
+        <v>138</v>
+      </c>
+      <c r="D85" t="s">
+        <v>36</v>
+      </c>
+      <c r="E85" t="s">
+        <v>45</v>
+      </c>
+      <c r="F85" t="s">
+        <v>48</v>
+      </c>
+      <c r="G85" t="s">
+        <v>271</v>
+      </c>
+      <c r="I85" t="s">
+        <v>328</v>
+      </c>
+      <c r="J85" t="s">
+        <v>10</v>
+      </c>
+      <c r="L85">
+        <v>5000</v>
+      </c>
+      <c r="P85" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>2026</v>
+      </c>
+      <c r="B86">
+        <v>6</v>
+      </c>
+      <c r="C86" t="s">
+        <v>138</v>
+      </c>
+      <c r="D86" t="s">
+        <v>27</v>
+      </c>
+      <c r="E86" t="s">
+        <v>503</v>
+      </c>
+      <c r="F86" t="s">
+        <v>48</v>
+      </c>
+      <c r="G86" t="s">
+        <v>122</v>
+      </c>
+      <c r="I86" t="s">
+        <v>29</v>
+      </c>
+      <c r="J86" t="s">
+        <v>88</v>
+      </c>
+      <c r="P86" t="s">
+        <v>550</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2761" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7D1B7AD-5A3F-4E9D-8160-BC68DCB9DC10}"/>
+  <xr:revisionPtr revIDLastSave="2858" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0558C2F8-45AF-4259-BC93-8BF1AA9B1FC4}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11088" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11202" uniqueCount="558">
   <si>
     <t>Year</t>
   </si>
@@ -1682,6 +1682,24 @@
   </si>
   <si>
     <t>10,000 of fine suspended for period of 12 months subject to no further breach of this regulation</t>
+  </si>
+  <si>
+    <t>Out of position at start</t>
+  </si>
+  <si>
+    <t>Out of position at restart. Penalty applied after race.</t>
+  </si>
+  <si>
+    <t>Mechanics working on car during red flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap of over 10 car lengths </t>
+  </si>
+  <si>
+    <t>Recon laps. Driver's first reprimand of the season</t>
+  </si>
+  <si>
+    <t>Applied after race</t>
   </si>
 </sst>
 </file>
@@ -45826,7 +45844,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -48716,6 +48734,495 @@
         <v>550</v>
       </c>
     </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>2026</v>
+      </c>
+      <c r="B87">
+        <v>6</v>
+      </c>
+      <c r="C87" t="s">
+        <v>138</v>
+      </c>
+      <c r="D87" t="s">
+        <v>23</v>
+      </c>
+      <c r="E87" t="s">
+        <v>509</v>
+      </c>
+      <c r="F87" t="s">
+        <v>49</v>
+      </c>
+      <c r="G87" t="s">
+        <v>272</v>
+      </c>
+      <c r="J87" t="s">
+        <v>331</v>
+      </c>
+      <c r="O87" t="s">
+        <v>552</v>
+      </c>
+      <c r="P87" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>2026</v>
+      </c>
+      <c r="B88">
+        <v>6</v>
+      </c>
+      <c r="C88" t="s">
+        <v>138</v>
+      </c>
+      <c r="D88" t="s">
+        <v>24</v>
+      </c>
+      <c r="E88" t="s">
+        <v>41</v>
+      </c>
+      <c r="F88" t="s">
+        <v>49</v>
+      </c>
+      <c r="G88" t="s">
+        <v>270</v>
+      </c>
+      <c r="J88" t="s">
+        <v>82</v>
+      </c>
+      <c r="K88">
+        <v>5</v>
+      </c>
+      <c r="P88" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>2026</v>
+      </c>
+      <c r="B89">
+        <v>6</v>
+      </c>
+      <c r="C89" t="s">
+        <v>138</v>
+      </c>
+      <c r="D89" t="s">
+        <v>37</v>
+      </c>
+      <c r="E89" t="s">
+        <v>38</v>
+      </c>
+      <c r="F89" t="s">
+        <v>49</v>
+      </c>
+      <c r="G89" t="s">
+        <v>270</v>
+      </c>
+      <c r="J89" t="s">
+        <v>82</v>
+      </c>
+      <c r="K89">
+        <v>5</v>
+      </c>
+      <c r="P89" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>2026</v>
+      </c>
+      <c r="B90">
+        <v>6</v>
+      </c>
+      <c r="C90" t="s">
+        <v>138</v>
+      </c>
+      <c r="D90" t="s">
+        <v>215</v>
+      </c>
+      <c r="E90" t="s">
+        <v>149</v>
+      </c>
+      <c r="F90" t="s">
+        <v>49</v>
+      </c>
+      <c r="G90" t="s">
+        <v>270</v>
+      </c>
+      <c r="J90" t="s">
+        <v>82</v>
+      </c>
+      <c r="K90">
+        <v>5</v>
+      </c>
+      <c r="P90" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>2026</v>
+      </c>
+      <c r="B91">
+        <v>6</v>
+      </c>
+      <c r="C91" t="s">
+        <v>138</v>
+      </c>
+      <c r="D91" t="s">
+        <v>25</v>
+      </c>
+      <c r="E91" t="s">
+        <v>149</v>
+      </c>
+      <c r="F91" t="s">
+        <v>49</v>
+      </c>
+      <c r="G91" t="s">
+        <v>270</v>
+      </c>
+      <c r="J91" t="s">
+        <v>82</v>
+      </c>
+      <c r="K91">
+        <v>5</v>
+      </c>
+      <c r="P91" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>2026</v>
+      </c>
+      <c r="B92">
+        <v>6</v>
+      </c>
+      <c r="C92" t="s">
+        <v>138</v>
+      </c>
+      <c r="D92" t="s">
+        <v>192</v>
+      </c>
+      <c r="E92" t="s">
+        <v>42</v>
+      </c>
+      <c r="F92" t="s">
+        <v>49</v>
+      </c>
+      <c r="G92" t="s">
+        <v>270</v>
+      </c>
+      <c r="J92" t="s">
+        <v>82</v>
+      </c>
+      <c r="K92">
+        <v>5</v>
+      </c>
+      <c r="P92" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>2026</v>
+      </c>
+      <c r="B93">
+        <v>6</v>
+      </c>
+      <c r="C93" t="s">
+        <v>138</v>
+      </c>
+      <c r="D93" t="s">
+        <v>25</v>
+      </c>
+      <c r="E93" t="s">
+        <v>149</v>
+      </c>
+      <c r="F93" t="s">
+        <v>49</v>
+      </c>
+      <c r="G93" t="s">
+        <v>270</v>
+      </c>
+      <c r="J93" t="s">
+        <v>82</v>
+      </c>
+      <c r="K93">
+        <v>5</v>
+      </c>
+      <c r="P93" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>2026</v>
+      </c>
+      <c r="B94">
+        <v>6</v>
+      </c>
+      <c r="C94" t="s">
+        <v>138</v>
+      </c>
+      <c r="D94" t="s">
+        <v>28</v>
+      </c>
+      <c r="E94" t="s">
+        <v>147</v>
+      </c>
+      <c r="F94" t="s">
+        <v>49</v>
+      </c>
+      <c r="G94" t="s">
+        <v>124</v>
+      </c>
+      <c r="J94" t="s">
+        <v>82</v>
+      </c>
+      <c r="K94">
+        <v>5</v>
+      </c>
+      <c r="P94" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>2026</v>
+      </c>
+      <c r="B95">
+        <v>6</v>
+      </c>
+      <c r="C95" t="s">
+        <v>138</v>
+      </c>
+      <c r="D95" t="s">
+        <v>23</v>
+      </c>
+      <c r="E95" t="s">
+        <v>509</v>
+      </c>
+      <c r="F95" t="s">
+        <v>49</v>
+      </c>
+      <c r="G95" t="s">
+        <v>272</v>
+      </c>
+      <c r="J95" t="s">
+        <v>82</v>
+      </c>
+      <c r="K95">
+        <v>10</v>
+      </c>
+      <c r="O95" t="s">
+        <v>553</v>
+      </c>
+      <c r="P95" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>2026</v>
+      </c>
+      <c r="B96">
+        <v>6</v>
+      </c>
+      <c r="C96" t="s">
+        <v>138</v>
+      </c>
+      <c r="D96" t="s">
+        <v>214</v>
+      </c>
+      <c r="E96" t="s">
+        <v>40</v>
+      </c>
+      <c r="F96" t="s">
+        <v>49</v>
+      </c>
+      <c r="G96" t="s">
+        <v>197</v>
+      </c>
+      <c r="J96" t="s">
+        <v>282</v>
+      </c>
+      <c r="O96" t="s">
+        <v>554</v>
+      </c>
+      <c r="P96" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>2026</v>
+      </c>
+      <c r="B97">
+        <v>6</v>
+      </c>
+      <c r="C97" t="s">
+        <v>138</v>
+      </c>
+      <c r="D97" t="s">
+        <v>214</v>
+      </c>
+      <c r="E97" t="s">
+        <v>40</v>
+      </c>
+      <c r="F97" t="s">
+        <v>49</v>
+      </c>
+      <c r="G97" t="s">
+        <v>117</v>
+      </c>
+      <c r="J97" t="s">
+        <v>282</v>
+      </c>
+      <c r="O97" t="s">
+        <v>555</v>
+      </c>
+      <c r="P97" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>2026</v>
+      </c>
+      <c r="B98">
+        <v>6</v>
+      </c>
+      <c r="C98" t="s">
+        <v>138</v>
+      </c>
+      <c r="D98" t="s">
+        <v>24</v>
+      </c>
+      <c r="E98" t="s">
+        <v>41</v>
+      </c>
+      <c r="F98" t="s">
+        <v>49</v>
+      </c>
+      <c r="G98" t="s">
+        <v>117</v>
+      </c>
+      <c r="J98" t="s">
+        <v>282</v>
+      </c>
+      <c r="O98" t="s">
+        <v>555</v>
+      </c>
+      <c r="P98" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>2026</v>
+      </c>
+      <c r="B99">
+        <v>6</v>
+      </c>
+      <c r="C99" t="s">
+        <v>138</v>
+      </c>
+      <c r="D99" t="s">
+        <v>23</v>
+      </c>
+      <c r="E99" t="s">
+        <v>509</v>
+      </c>
+      <c r="F99" t="s">
+        <v>219</v>
+      </c>
+      <c r="G99" t="s">
+        <v>122</v>
+      </c>
+      <c r="J99" t="s">
+        <v>81</v>
+      </c>
+      <c r="O99" t="s">
+        <v>556</v>
+      </c>
+      <c r="P99" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>2026</v>
+      </c>
+      <c r="B100">
+        <v>6</v>
+      </c>
+      <c r="C100" t="s">
+        <v>138</v>
+      </c>
+      <c r="D100" t="s">
+        <v>27</v>
+      </c>
+      <c r="E100" t="s">
+        <v>503</v>
+      </c>
+      <c r="F100" t="s">
+        <v>49</v>
+      </c>
+      <c r="G100" t="s">
+        <v>263</v>
+      </c>
+      <c r="I100" t="s">
+        <v>108</v>
+      </c>
+      <c r="J100" t="s">
+        <v>82</v>
+      </c>
+      <c r="K100">
+        <v>10</v>
+      </c>
+      <c r="O100" t="s">
+        <v>557</v>
+      </c>
+      <c r="P100" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>2026</v>
+      </c>
+      <c r="B101">
+        <v>6</v>
+      </c>
+      <c r="C101" t="s">
+        <v>138</v>
+      </c>
+      <c r="D101" t="s">
+        <v>215</v>
+      </c>
+      <c r="E101" t="s">
+        <v>149</v>
+      </c>
+      <c r="F101" t="s">
+        <v>49</v>
+      </c>
+      <c r="G101" t="s">
+        <v>263</v>
+      </c>
+      <c r="I101" t="s">
+        <v>108</v>
+      </c>
+      <c r="J101" t="s">
+        <v>282</v>
+      </c>
+      <c r="P101" t="s">
+        <v>550</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2858" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0558C2F8-45AF-4259-BC93-8BF1AA9B1FC4}"/>
+  <xr:revisionPtr revIDLastSave="2868" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0207AF6A-288E-49F7-AF59-F5F1D85081AE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11202" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11209" uniqueCount="558">
   <si>
     <t>Year</t>
   </si>
@@ -45844,7 +45844,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P101"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -49223,6 +49223,35 @@
         <v>550</v>
       </c>
     </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>2026</v>
+      </c>
+      <c r="B102">
+        <v>6</v>
+      </c>
+      <c r="C102" t="s">
+        <v>138</v>
+      </c>
+      <c r="D102" t="s">
+        <v>37</v>
+      </c>
+      <c r="E102" t="s">
+        <v>38</v>
+      </c>
+      <c r="F102" t="s">
+        <v>49</v>
+      </c>
+      <c r="G102" t="s">
+        <v>342</v>
+      </c>
+      <c r="J102" t="s">
+        <v>331</v>
+      </c>
+      <c r="P102" t="s">
+        <v>550</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2868" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0207AF6A-288E-49F7-AF59-F5F1D85081AE}"/>
+  <xr:revisionPtr revIDLastSave="2911" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B47B7E5E-E7B3-45E4-B6CB-E975B70D75DA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11209" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11247" uniqueCount="564">
   <si>
     <t>Year</t>
   </si>
@@ -1700,6 +1700,24 @@
   </si>
   <si>
     <t>Applied after race</t>
+  </si>
+  <si>
+    <t>Overturned on Review</t>
+  </si>
+  <si>
+    <t>5 second time penalty overturned post race on review</t>
+  </si>
+  <si>
+    <t>Crossed the white line at pit exit</t>
+  </si>
+  <si>
+    <t>Felix Holter, Natalie Corsmit, Kipras Aleknavicius, Derek Warwick, David Domingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fine </t>
+  </si>
+  <si>
+    <t>Drivers first reprimand of the season</t>
   </si>
 </sst>
 </file>
@@ -45844,7 +45862,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P102"/>
+  <dimension ref="A1:P107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -48949,10 +48967,10 @@
         <v>270</v>
       </c>
       <c r="J93" t="s">
-        <v>82</v>
-      </c>
-      <c r="K93">
-        <v>5</v>
+        <v>558</v>
+      </c>
+      <c r="O93" t="s">
+        <v>559</v>
       </c>
       <c r="P93" t="s">
         <v>550</v>
@@ -49250,6 +49268,166 @@
       </c>
       <c r="P102" t="s">
         <v>550</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>2026</v>
+      </c>
+      <c r="B103">
+        <v>7</v>
+      </c>
+      <c r="C103" t="s">
+        <v>96</v>
+      </c>
+      <c r="D103" t="s">
+        <v>32</v>
+      </c>
+      <c r="E103" t="s">
+        <v>147</v>
+      </c>
+      <c r="F103" t="s">
+        <v>531</v>
+      </c>
+      <c r="G103" t="s">
+        <v>120</v>
+      </c>
+      <c r="H103" t="s">
+        <v>560</v>
+      </c>
+      <c r="J103" t="s">
+        <v>88</v>
+      </c>
+      <c r="P103" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>2026</v>
+      </c>
+      <c r="B104">
+        <v>7</v>
+      </c>
+      <c r="C104" t="s">
+        <v>96</v>
+      </c>
+      <c r="D104" t="s">
+        <v>463</v>
+      </c>
+      <c r="E104" t="s">
+        <v>509</v>
+      </c>
+      <c r="F104" t="s">
+        <v>531</v>
+      </c>
+      <c r="G104" t="s">
+        <v>270</v>
+      </c>
+      <c r="J104" t="s">
+        <v>10</v>
+      </c>
+      <c r="L104">
+        <v>100</v>
+      </c>
+      <c r="P104" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>2026</v>
+      </c>
+      <c r="B105">
+        <v>7</v>
+      </c>
+      <c r="C105" t="s">
+        <v>96</v>
+      </c>
+      <c r="D105" t="s">
+        <v>23</v>
+      </c>
+      <c r="E105" t="s">
+        <v>509</v>
+      </c>
+      <c r="F105" t="s">
+        <v>531</v>
+      </c>
+      <c r="G105" t="s">
+        <v>270</v>
+      </c>
+      <c r="J105" t="s">
+        <v>562</v>
+      </c>
+      <c r="L105">
+        <v>500</v>
+      </c>
+      <c r="P105" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>2026</v>
+      </c>
+      <c r="B106">
+        <v>7</v>
+      </c>
+      <c r="C106" t="s">
+        <v>96</v>
+      </c>
+      <c r="D106" t="s">
+        <v>28</v>
+      </c>
+      <c r="E106" t="s">
+        <v>147</v>
+      </c>
+      <c r="F106" t="s">
+        <v>532</v>
+      </c>
+      <c r="G106" t="s">
+        <v>270</v>
+      </c>
+      <c r="J106" t="s">
+        <v>10</v>
+      </c>
+      <c r="L106">
+        <v>600</v>
+      </c>
+      <c r="P106" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>2026</v>
+      </c>
+      <c r="B107">
+        <v>7</v>
+      </c>
+      <c r="C107" t="s">
+        <v>96</v>
+      </c>
+      <c r="D107" t="s">
+        <v>259</v>
+      </c>
+      <c r="E107" t="s">
+        <v>38</v>
+      </c>
+      <c r="F107" t="s">
+        <v>532</v>
+      </c>
+      <c r="G107" t="s">
+        <v>264</v>
+      </c>
+      <c r="J107" t="s">
+        <v>81</v>
+      </c>
+      <c r="O107" t="s">
+        <v>563</v>
+      </c>
+      <c r="P107" t="s">
+        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2911" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B47B7E5E-E7B3-45E4-B6CB-E975B70D75DA}"/>
+  <xr:revisionPtr revIDLastSave="2921" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA492794-2561-465C-831D-F930F1308358}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11247" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11255" uniqueCount="564">
   <si>
     <t>Year</t>
   </si>
@@ -45862,7 +45862,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P107"/>
+  <dimension ref="A1:P108"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -49430,6 +49430,38 @@
         <v>561</v>
       </c>
     </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>2026</v>
+      </c>
+      <c r="B108">
+        <v>7</v>
+      </c>
+      <c r="C108" t="s">
+        <v>96</v>
+      </c>
+      <c r="D108" t="s">
+        <v>29</v>
+      </c>
+      <c r="E108" t="s">
+        <v>41</v>
+      </c>
+      <c r="F108" t="s">
+        <v>532</v>
+      </c>
+      <c r="G108" t="s">
+        <v>53</v>
+      </c>
+      <c r="I108" t="s">
+        <v>27</v>
+      </c>
+      <c r="J108" t="s">
+        <v>88</v>
+      </c>
+      <c r="P108" t="s">
+        <v>561</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2921" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA492794-2561-465C-831D-F930F1308358}"/>
+  <xr:revisionPtr revIDLastSave="2969" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{664969AF-92A8-44CE-9AFC-9CA562D573B0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11255" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11307" uniqueCount="566">
   <si>
     <t>Year</t>
   </si>
@@ -1718,6 +1718,12 @@
   </si>
   <si>
     <t>Drivers first reprimand of the season</t>
+  </si>
+  <si>
+    <t>Tire blankets left on</t>
+  </si>
+  <si>
+    <t>Equipment left out</t>
   </si>
 </sst>
 </file>
@@ -45862,7 +45868,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P108"/>
+  <dimension ref="A1:P115"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -49462,6 +49468,233 @@
         <v>561</v>
       </c>
     </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>2026</v>
+      </c>
+      <c r="B109">
+        <v>7</v>
+      </c>
+      <c r="C109" t="s">
+        <v>96</v>
+      </c>
+      <c r="D109" t="s">
+        <v>32</v>
+      </c>
+      <c r="E109" t="s">
+        <v>147</v>
+      </c>
+      <c r="F109" t="s">
+        <v>48</v>
+      </c>
+      <c r="G109" t="s">
+        <v>113</v>
+      </c>
+      <c r="J109" t="s">
+        <v>11</v>
+      </c>
+      <c r="M109" t="s">
+        <v>242</v>
+      </c>
+      <c r="P109" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>2026</v>
+      </c>
+      <c r="B110">
+        <v>7</v>
+      </c>
+      <c r="C110" t="s">
+        <v>96</v>
+      </c>
+      <c r="D110" t="s">
+        <v>27</v>
+      </c>
+      <c r="E110" t="s">
+        <v>503</v>
+      </c>
+      <c r="F110" t="s">
+        <v>49</v>
+      </c>
+      <c r="G110" t="s">
+        <v>335</v>
+      </c>
+      <c r="J110" t="s">
+        <v>282</v>
+      </c>
+      <c r="P110" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>2026</v>
+      </c>
+      <c r="B111">
+        <v>7</v>
+      </c>
+      <c r="C111" t="s">
+        <v>96</v>
+      </c>
+      <c r="D111" t="s">
+        <v>328</v>
+      </c>
+      <c r="E111" t="s">
+        <v>262</v>
+      </c>
+      <c r="F111" t="s">
+        <v>49</v>
+      </c>
+      <c r="G111" t="s">
+        <v>335</v>
+      </c>
+      <c r="J111" t="s">
+        <v>282</v>
+      </c>
+      <c r="P111" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>2026</v>
+      </c>
+      <c r="B112">
+        <v>7</v>
+      </c>
+      <c r="C112" t="s">
+        <v>96</v>
+      </c>
+      <c r="D112" t="s">
+        <v>215</v>
+      </c>
+      <c r="E112" t="s">
+        <v>149</v>
+      </c>
+      <c r="F112" t="s">
+        <v>49</v>
+      </c>
+      <c r="G112" t="s">
+        <v>111</v>
+      </c>
+      <c r="J112" t="s">
+        <v>80</v>
+      </c>
+      <c r="K112">
+        <v>10</v>
+      </c>
+      <c r="N112">
+        <v>1</v>
+      </c>
+      <c r="P112" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>2026</v>
+      </c>
+      <c r="B113">
+        <v>7</v>
+      </c>
+      <c r="C113" t="s">
+        <v>96</v>
+      </c>
+      <c r="D113" t="s">
+        <v>36</v>
+      </c>
+      <c r="E113" t="s">
+        <v>45</v>
+      </c>
+      <c r="F113" t="s">
+        <v>49</v>
+      </c>
+      <c r="G113" t="s">
+        <v>504</v>
+      </c>
+      <c r="H113" t="s">
+        <v>564</v>
+      </c>
+      <c r="J113" t="s">
+        <v>10</v>
+      </c>
+      <c r="L113">
+        <v>5000</v>
+      </c>
+      <c r="P113" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>2026</v>
+      </c>
+      <c r="B114">
+        <v>7</v>
+      </c>
+      <c r="C114" t="s">
+        <v>96</v>
+      </c>
+      <c r="D114" t="s">
+        <v>108</v>
+      </c>
+      <c r="E114" t="s">
+        <v>45</v>
+      </c>
+      <c r="F114" t="s">
+        <v>49</v>
+      </c>
+      <c r="G114" t="s">
+        <v>504</v>
+      </c>
+      <c r="H114" t="s">
+        <v>565</v>
+      </c>
+      <c r="J114" t="s">
+        <v>10</v>
+      </c>
+      <c r="L114">
+        <v>5000</v>
+      </c>
+      <c r="P114" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>2026</v>
+      </c>
+      <c r="B115">
+        <v>7</v>
+      </c>
+      <c r="C115" t="s">
+        <v>96</v>
+      </c>
+      <c r="D115" t="s">
+        <v>259</v>
+      </c>
+      <c r="E115" t="s">
+        <v>38</v>
+      </c>
+      <c r="F115" t="s">
+        <v>49</v>
+      </c>
+      <c r="G115" t="s">
+        <v>124</v>
+      </c>
+      <c r="J115" t="s">
+        <v>82</v>
+      </c>
+      <c r="K115">
+        <v>5</v>
+      </c>
+      <c r="P115" t="s">
+        <v>561</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2969" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{664969AF-92A8-44CE-9AFC-9CA562D573B0}"/>
+  <xr:revisionPtr revIDLastSave="3049" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78464944-42BE-489E-BDA0-FC9791276FE8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11307" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11372" uniqueCount="568">
   <si>
     <t>Year</t>
   </si>
@@ -1724,6 +1724,12 @@
   </si>
   <si>
     <t>Equipment left out</t>
+  </si>
+  <si>
+    <t>Felix Holter, Loic Bacquelaine, Pedro Lamy, Wilhelm Singer</t>
+  </si>
+  <si>
+    <t>No doc on FIA website</t>
   </si>
 </sst>
 </file>
@@ -45868,7 +45874,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P115"/>
+  <dimension ref="A1:P124"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -49695,6 +49701,276 @@
         <v>561</v>
       </c>
     </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>2026</v>
+      </c>
+      <c r="B116">
+        <v>8</v>
+      </c>
+      <c r="C116" t="s">
+        <v>91</v>
+      </c>
+      <c r="D116" t="s">
+        <v>32</v>
+      </c>
+      <c r="E116" t="s">
+        <v>147</v>
+      </c>
+      <c r="F116" t="s">
+        <v>49</v>
+      </c>
+      <c r="G116" t="s">
+        <v>270</v>
+      </c>
+      <c r="J116" t="s">
+        <v>82</v>
+      </c>
+      <c r="K116">
+        <v>5</v>
+      </c>
+      <c r="P116" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>2026</v>
+      </c>
+      <c r="B117">
+        <v>8</v>
+      </c>
+      <c r="C117" t="s">
+        <v>91</v>
+      </c>
+      <c r="D117" t="s">
+        <v>214</v>
+      </c>
+      <c r="E117" t="s">
+        <v>40</v>
+      </c>
+      <c r="F117" t="s">
+        <v>48</v>
+      </c>
+      <c r="G117" t="s">
+        <v>122</v>
+      </c>
+      <c r="J117" t="s">
+        <v>88</v>
+      </c>
+      <c r="P117" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>2026</v>
+      </c>
+      <c r="B118">
+        <v>8</v>
+      </c>
+      <c r="C118" t="s">
+        <v>91</v>
+      </c>
+      <c r="D118" t="s">
+        <v>192</v>
+      </c>
+      <c r="E118" t="s">
+        <v>42</v>
+      </c>
+      <c r="F118" t="s">
+        <v>219</v>
+      </c>
+      <c r="G118" t="s">
+        <v>122</v>
+      </c>
+      <c r="J118" t="s">
+        <v>282</v>
+      </c>
+      <c r="O118" t="s">
+        <v>136</v>
+      </c>
+      <c r="P118" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>2026</v>
+      </c>
+      <c r="B119">
+        <v>8</v>
+      </c>
+      <c r="C119" t="s">
+        <v>91</v>
+      </c>
+      <c r="D119" t="s">
+        <v>194</v>
+      </c>
+      <c r="E119" t="s">
+        <v>262</v>
+      </c>
+      <c r="F119" t="s">
+        <v>49</v>
+      </c>
+      <c r="G119" t="s">
+        <v>122</v>
+      </c>
+      <c r="J119" t="s">
+        <v>282</v>
+      </c>
+      <c r="P119" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>2026</v>
+      </c>
+      <c r="B120">
+        <v>8</v>
+      </c>
+      <c r="C120" t="s">
+        <v>91</v>
+      </c>
+      <c r="D120" t="s">
+        <v>36</v>
+      </c>
+      <c r="E120" t="s">
+        <v>45</v>
+      </c>
+      <c r="F120" t="s">
+        <v>49</v>
+      </c>
+      <c r="G120" t="s">
+        <v>111</v>
+      </c>
+      <c r="J120" t="s">
+        <v>282</v>
+      </c>
+      <c r="P120" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>2026</v>
+      </c>
+      <c r="B121">
+        <v>8</v>
+      </c>
+      <c r="C121" t="s">
+        <v>91</v>
+      </c>
+      <c r="D121" t="s">
+        <v>28</v>
+      </c>
+      <c r="E121" t="s">
+        <v>147</v>
+      </c>
+      <c r="F121" t="s">
+        <v>49</v>
+      </c>
+      <c r="G121" t="s">
+        <v>313</v>
+      </c>
+      <c r="J121" t="s">
+        <v>282</v>
+      </c>
+      <c r="P121" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>2026</v>
+      </c>
+      <c r="B122">
+        <v>8</v>
+      </c>
+      <c r="C122" t="s">
+        <v>91</v>
+      </c>
+      <c r="D122" t="s">
+        <v>32</v>
+      </c>
+      <c r="E122" t="s">
+        <v>147</v>
+      </c>
+      <c r="F122" t="s">
+        <v>49</v>
+      </c>
+      <c r="G122" t="s">
+        <v>313</v>
+      </c>
+      <c r="J122" t="s">
+        <v>282</v>
+      </c>
+      <c r="P122" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>2026</v>
+      </c>
+      <c r="B123">
+        <v>8</v>
+      </c>
+      <c r="C123" t="s">
+        <v>91</v>
+      </c>
+      <c r="D123" t="s">
+        <v>23</v>
+      </c>
+      <c r="E123" t="s">
+        <v>509</v>
+      </c>
+      <c r="F123" t="s">
+        <v>49</v>
+      </c>
+      <c r="G123" t="s">
+        <v>272</v>
+      </c>
+      <c r="J123" t="s">
+        <v>282</v>
+      </c>
+      <c r="P123" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>2026</v>
+      </c>
+      <c r="B124">
+        <v>8</v>
+      </c>
+      <c r="C124" t="s">
+        <v>91</v>
+      </c>
+      <c r="D124" t="s">
+        <v>37</v>
+      </c>
+      <c r="E124" t="s">
+        <v>38</v>
+      </c>
+      <c r="F124" t="s">
+        <v>48</v>
+      </c>
+      <c r="G124" t="s">
+        <v>111</v>
+      </c>
+      <c r="J124" t="s">
+        <v>282</v>
+      </c>
+      <c r="O124" t="s">
+        <v>567</v>
+      </c>
+      <c r="P124" t="s">
+        <v>566</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3049" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78464944-42BE-489E-BDA0-FC9791276FE8}"/>
+  <xr:revisionPtr revIDLastSave="3171" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57DC72CB-067B-4A61-8B47-55C1F743F473}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11372" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11510" uniqueCount="574">
   <si>
     <t>Year</t>
   </si>
@@ -1730,6 +1730,24 @@
   </si>
   <si>
     <t>No doc on FIA website</t>
+  </si>
+  <si>
+    <t>Overtaking the safety car</t>
+  </si>
+  <si>
+    <t>Penalty Lap</t>
+  </si>
+  <si>
+    <t>1 Penalty Lap</t>
+  </si>
+  <si>
+    <t>Gerd Ennser, Mathieu Remmerie, Richard Norbury, Tanja Geilhausen, Pedro Lamy</t>
+  </si>
+  <si>
+    <t>Abnormal change of direction</t>
+  </si>
+  <si>
+    <t>Imposed after race</t>
   </si>
 </sst>
 </file>
@@ -45874,7 +45892,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P124"/>
+  <dimension ref="A1:P142"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -49971,6 +49989,597 @@
         <v>566</v>
       </c>
     </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>2026</v>
+      </c>
+      <c r="B125">
+        <v>9</v>
+      </c>
+      <c r="C125" t="s">
+        <v>94</v>
+      </c>
+      <c r="D125" t="s">
+        <v>108</v>
+      </c>
+      <c r="E125" t="s">
+        <v>45</v>
+      </c>
+      <c r="F125" t="s">
+        <v>49</v>
+      </c>
+      <c r="G125" t="s">
+        <v>117</v>
+      </c>
+      <c r="H125" t="s">
+        <v>568</v>
+      </c>
+      <c r="J125" t="s">
+        <v>569</v>
+      </c>
+      <c r="O125" t="s">
+        <v>570</v>
+      </c>
+      <c r="P125" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>2026</v>
+      </c>
+      <c r="B126">
+        <v>9</v>
+      </c>
+      <c r="C126" t="s">
+        <v>94</v>
+      </c>
+      <c r="D126" t="s">
+        <v>24</v>
+      </c>
+      <c r="E126" t="s">
+        <v>41</v>
+      </c>
+      <c r="F126" t="s">
+        <v>49</v>
+      </c>
+      <c r="G126" t="s">
+        <v>111</v>
+      </c>
+      <c r="J126" t="s">
+        <v>81</v>
+      </c>
+      <c r="O126" t="s">
+        <v>543</v>
+      </c>
+      <c r="P126" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>2026</v>
+      </c>
+      <c r="B127">
+        <v>9</v>
+      </c>
+      <c r="C127" t="s">
+        <v>94</v>
+      </c>
+      <c r="D127" t="s">
+        <v>24</v>
+      </c>
+      <c r="E127" t="s">
+        <v>41</v>
+      </c>
+      <c r="F127" t="s">
+        <v>49</v>
+      </c>
+      <c r="G127" t="s">
+        <v>272</v>
+      </c>
+      <c r="J127" t="s">
+        <v>82</v>
+      </c>
+      <c r="K127">
+        <v>5</v>
+      </c>
+      <c r="P127" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>2026</v>
+      </c>
+      <c r="B128">
+        <v>9</v>
+      </c>
+      <c r="C128" t="s">
+        <v>94</v>
+      </c>
+      <c r="D128" t="s">
+        <v>328</v>
+      </c>
+      <c r="E128" t="s">
+        <v>262</v>
+      </c>
+      <c r="F128" t="s">
+        <v>48</v>
+      </c>
+      <c r="G128" t="s">
+        <v>233</v>
+      </c>
+      <c r="J128" t="s">
+        <v>10</v>
+      </c>
+      <c r="L128">
+        <v>5000</v>
+      </c>
+      <c r="P128" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>2026</v>
+      </c>
+      <c r="B129">
+        <v>9</v>
+      </c>
+      <c r="C129" t="s">
+        <v>94</v>
+      </c>
+      <c r="D129" t="s">
+        <v>328</v>
+      </c>
+      <c r="E129" t="s">
+        <v>262</v>
+      </c>
+      <c r="F129" t="s">
+        <v>150</v>
+      </c>
+      <c r="G129" t="s">
+        <v>122</v>
+      </c>
+      <c r="H129" t="s">
+        <v>537</v>
+      </c>
+      <c r="J129" t="s">
+        <v>88</v>
+      </c>
+      <c r="P129" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>2026</v>
+      </c>
+      <c r="B130">
+        <v>9</v>
+      </c>
+      <c r="C130" t="s">
+        <v>94</v>
+      </c>
+      <c r="D130" t="s">
+        <v>194</v>
+      </c>
+      <c r="E130" t="s">
+        <v>262</v>
+      </c>
+      <c r="F130" t="s">
+        <v>174</v>
+      </c>
+      <c r="G130" t="s">
+        <v>264</v>
+      </c>
+      <c r="H130" t="s">
+        <v>572</v>
+      </c>
+      <c r="J130" t="s">
+        <v>88</v>
+      </c>
+      <c r="P130" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>2026</v>
+      </c>
+      <c r="B131">
+        <v>9</v>
+      </c>
+      <c r="C131" t="s">
+        <v>94</v>
+      </c>
+      <c r="D131" t="s">
+        <v>27</v>
+      </c>
+      <c r="E131" t="s">
+        <v>503</v>
+      </c>
+      <c r="F131" t="s">
+        <v>174</v>
+      </c>
+      <c r="G131" t="s">
+        <v>335</v>
+      </c>
+      <c r="I131" t="s">
+        <v>30</v>
+      </c>
+      <c r="J131" t="s">
+        <v>82</v>
+      </c>
+      <c r="K131">
+        <v>5</v>
+      </c>
+      <c r="O131" t="s">
+        <v>573</v>
+      </c>
+      <c r="P131" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>2026</v>
+      </c>
+      <c r="B132">
+        <v>9</v>
+      </c>
+      <c r="C132" t="s">
+        <v>94</v>
+      </c>
+      <c r="D132" t="s">
+        <v>36</v>
+      </c>
+      <c r="E132" t="s">
+        <v>45</v>
+      </c>
+      <c r="F132" t="s">
+        <v>150</v>
+      </c>
+      <c r="G132" t="s">
+        <v>122</v>
+      </c>
+      <c r="H132" t="s">
+        <v>537</v>
+      </c>
+      <c r="J132" t="s">
+        <v>88</v>
+      </c>
+      <c r="P132" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>2026</v>
+      </c>
+      <c r="B133">
+        <v>9</v>
+      </c>
+      <c r="C133" t="s">
+        <v>94</v>
+      </c>
+      <c r="D133" t="s">
+        <v>36</v>
+      </c>
+      <c r="E133" t="s">
+        <v>45</v>
+      </c>
+      <c r="F133" t="s">
+        <v>150</v>
+      </c>
+      <c r="G133" t="s">
+        <v>66</v>
+      </c>
+      <c r="J133" t="s">
+        <v>11</v>
+      </c>
+      <c r="M133" t="s">
+        <v>242</v>
+      </c>
+      <c r="P133" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <v>2026</v>
+      </c>
+      <c r="B134">
+        <v>9</v>
+      </c>
+      <c r="C134" t="s">
+        <v>94</v>
+      </c>
+      <c r="D134" t="s">
+        <v>36</v>
+      </c>
+      <c r="E134" t="s">
+        <v>45</v>
+      </c>
+      <c r="F134" t="s">
+        <v>49</v>
+      </c>
+      <c r="G134" t="s">
+        <v>263</v>
+      </c>
+      <c r="I134" t="s">
+        <v>217</v>
+      </c>
+      <c r="J134" t="s">
+        <v>82</v>
+      </c>
+      <c r="K134">
+        <v>10</v>
+      </c>
+      <c r="P134" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>2026</v>
+      </c>
+      <c r="B135">
+        <v>9</v>
+      </c>
+      <c r="C135" t="s">
+        <v>94</v>
+      </c>
+      <c r="D135" t="s">
+        <v>28</v>
+      </c>
+      <c r="E135" t="s">
+        <v>147</v>
+      </c>
+      <c r="F135" t="s">
+        <v>48</v>
+      </c>
+      <c r="G135" t="s">
+        <v>113</v>
+      </c>
+      <c r="J135" t="s">
+        <v>11</v>
+      </c>
+      <c r="M135">
+        <v>10</v>
+      </c>
+      <c r="P135" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>2026</v>
+      </c>
+      <c r="B136">
+        <v>9</v>
+      </c>
+      <c r="C136" t="s">
+        <v>94</v>
+      </c>
+      <c r="D136" t="s">
+        <v>28</v>
+      </c>
+      <c r="E136" t="s">
+        <v>147</v>
+      </c>
+      <c r="F136" t="s">
+        <v>49</v>
+      </c>
+      <c r="G136" t="s">
+        <v>124</v>
+      </c>
+      <c r="J136" t="s">
+        <v>82</v>
+      </c>
+      <c r="K136">
+        <v>5</v>
+      </c>
+      <c r="P136" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>2026</v>
+      </c>
+      <c r="B137">
+        <v>9</v>
+      </c>
+      <c r="C137" t="s">
+        <v>94</v>
+      </c>
+      <c r="D137" t="s">
+        <v>28</v>
+      </c>
+      <c r="E137" t="s">
+        <v>147</v>
+      </c>
+      <c r="F137" t="s">
+        <v>49</v>
+      </c>
+      <c r="G137" t="s">
+        <v>124</v>
+      </c>
+      <c r="J137" t="s">
+        <v>82</v>
+      </c>
+      <c r="K137">
+        <v>5</v>
+      </c>
+      <c r="P137" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>2026</v>
+      </c>
+      <c r="B138">
+        <v>9</v>
+      </c>
+      <c r="C138" t="s">
+        <v>94</v>
+      </c>
+      <c r="D138" t="s">
+        <v>28</v>
+      </c>
+      <c r="E138" t="s">
+        <v>147</v>
+      </c>
+      <c r="F138" t="s">
+        <v>49</v>
+      </c>
+      <c r="G138" t="s">
+        <v>124</v>
+      </c>
+      <c r="J138" t="s">
+        <v>82</v>
+      </c>
+      <c r="K138">
+        <v>5</v>
+      </c>
+      <c r="P138" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>2026</v>
+      </c>
+      <c r="B139">
+        <v>9</v>
+      </c>
+      <c r="C139" t="s">
+        <v>94</v>
+      </c>
+      <c r="D139" t="s">
+        <v>259</v>
+      </c>
+      <c r="E139" t="s">
+        <v>38</v>
+      </c>
+      <c r="F139" t="s">
+        <v>49</v>
+      </c>
+      <c r="G139" t="s">
+        <v>124</v>
+      </c>
+      <c r="J139" t="s">
+        <v>82</v>
+      </c>
+      <c r="K139">
+        <v>5</v>
+      </c>
+      <c r="P139" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>2026</v>
+      </c>
+      <c r="B140">
+        <v>9</v>
+      </c>
+      <c r="C140" t="s">
+        <v>94</v>
+      </c>
+      <c r="D140" t="s">
+        <v>23</v>
+      </c>
+      <c r="E140" t="s">
+        <v>509</v>
+      </c>
+      <c r="F140" t="s">
+        <v>174</v>
+      </c>
+      <c r="G140" t="s">
+        <v>263</v>
+      </c>
+      <c r="I140" t="s">
+        <v>32</v>
+      </c>
+      <c r="J140" t="s">
+        <v>82</v>
+      </c>
+      <c r="K140">
+        <v>10</v>
+      </c>
+      <c r="P140" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>2026</v>
+      </c>
+      <c r="B141">
+        <v>9</v>
+      </c>
+      <c r="C141" t="s">
+        <v>94</v>
+      </c>
+      <c r="D141" t="s">
+        <v>25</v>
+      </c>
+      <c r="E141" t="s">
+        <v>149</v>
+      </c>
+      <c r="F141" t="s">
+        <v>48</v>
+      </c>
+      <c r="G141" t="s">
+        <v>53</v>
+      </c>
+      <c r="I141" t="s">
+        <v>28</v>
+      </c>
+      <c r="J141" t="s">
+        <v>11</v>
+      </c>
+      <c r="M141">
+        <v>3</v>
+      </c>
+      <c r="P141" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>2026</v>
+      </c>
+      <c r="B142">
+        <v>9</v>
+      </c>
+      <c r="C142" t="s">
+        <v>94</v>
+      </c>
+      <c r="D142" t="s">
+        <v>30</v>
+      </c>
+      <c r="E142" t="s">
+        <v>39</v>
+      </c>
+      <c r="F142" t="s">
+        <v>48</v>
+      </c>
+      <c r="G142" t="s">
+        <v>111</v>
+      </c>
+      <c r="J142" t="s">
+        <v>282</v>
+      </c>
+      <c r="P142" t="s">
+        <v>571</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3171" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57DC72CB-067B-4A61-8B47-55C1F743F473}"/>
+  <xr:revisionPtr revIDLastSave="3280" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{832C8B2E-156E-4BF4-85BC-8E9ED21AE32E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11510" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11622" uniqueCount="584">
   <si>
     <t>Year</t>
   </si>
@@ -1748,6 +1748,36 @@
   </si>
   <si>
     <t>Imposed after race</t>
+  </si>
+  <si>
+    <t>Gerd Ennser, Matthew Selley, Alfonso Orihuela, Pedro Lamy, Loic Bacquelaine</t>
+  </si>
+  <si>
+    <t>Crossing the white line at pit entry</t>
+  </si>
+  <si>
+    <t>Late attending Thursday press conference</t>
+  </si>
+  <si>
+    <t>Jak Crawford</t>
+  </si>
+  <si>
+    <t>Failure to slow under double yellow flags</t>
+  </si>
+  <si>
+    <t>Left the pit lane without functioning rear lights</t>
+  </si>
+  <si>
+    <t>Driver's second reprimand of the season</t>
+  </si>
+  <si>
+    <t>Failure to return tires</t>
+  </si>
+  <si>
+    <t>Hit mechanic during pit stop</t>
+  </si>
+  <si>
+    <t>10000 of fine is suspended for 12 months</t>
   </si>
 </sst>
 </file>
@@ -45892,7 +45922,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P142"/>
+  <dimension ref="A1:P156"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -50580,6 +50610,481 @@
         <v>571</v>
       </c>
     </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>2026</v>
+      </c>
+      <c r="B143">
+        <v>10</v>
+      </c>
+      <c r="C143" t="s">
+        <v>97</v>
+      </c>
+      <c r="D143" t="s">
+        <v>108</v>
+      </c>
+      <c r="E143" t="s">
+        <v>45</v>
+      </c>
+      <c r="F143" t="s">
+        <v>48</v>
+      </c>
+      <c r="G143" t="s">
+        <v>113</v>
+      </c>
+      <c r="J143" t="s">
+        <v>11</v>
+      </c>
+      <c r="M143">
+        <v>10</v>
+      </c>
+      <c r="P143" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>2026</v>
+      </c>
+      <c r="B144">
+        <v>10</v>
+      </c>
+      <c r="C144" t="s">
+        <v>97</v>
+      </c>
+      <c r="D144" t="s">
+        <v>108</v>
+      </c>
+      <c r="E144" t="s">
+        <v>45</v>
+      </c>
+      <c r="F144" t="s">
+        <v>530</v>
+      </c>
+      <c r="G144" t="s">
+        <v>120</v>
+      </c>
+      <c r="H144" t="s">
+        <v>575</v>
+      </c>
+      <c r="J144" t="s">
+        <v>81</v>
+      </c>
+      <c r="O144" t="s">
+        <v>543</v>
+      </c>
+      <c r="P144" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>2026</v>
+      </c>
+      <c r="B145">
+        <v>10</v>
+      </c>
+      <c r="C145" t="s">
+        <v>97</v>
+      </c>
+      <c r="D145" t="s">
+        <v>30</v>
+      </c>
+      <c r="E145" t="s">
+        <v>39</v>
+      </c>
+      <c r="F145" t="s">
+        <v>219</v>
+      </c>
+      <c r="G145" t="s">
+        <v>199</v>
+      </c>
+      <c r="H145" t="s">
+        <v>576</v>
+      </c>
+      <c r="J145" t="s">
+        <v>10</v>
+      </c>
+      <c r="L145">
+        <v>5000</v>
+      </c>
+      <c r="O145" t="s">
+        <v>549</v>
+      </c>
+      <c r="P145" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <v>2026</v>
+      </c>
+      <c r="B146">
+        <v>10</v>
+      </c>
+      <c r="C146" t="s">
+        <v>97</v>
+      </c>
+      <c r="D146" t="s">
+        <v>24</v>
+      </c>
+      <c r="E146" t="s">
+        <v>41</v>
+      </c>
+      <c r="F146" t="s">
+        <v>49</v>
+      </c>
+      <c r="G146" t="s">
+        <v>263</v>
+      </c>
+      <c r="I146" t="s">
+        <v>37</v>
+      </c>
+      <c r="J146" t="s">
+        <v>82</v>
+      </c>
+      <c r="K146">
+        <v>5</v>
+      </c>
+      <c r="P146" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <v>2026</v>
+      </c>
+      <c r="B147">
+        <v>10</v>
+      </c>
+      <c r="C147" t="s">
+        <v>97</v>
+      </c>
+      <c r="D147" t="s">
+        <v>577</v>
+      </c>
+      <c r="E147" t="s">
+        <v>147</v>
+      </c>
+      <c r="F147" t="s">
+        <v>530</v>
+      </c>
+      <c r="G147" t="s">
+        <v>270</v>
+      </c>
+      <c r="J147" t="s">
+        <v>10</v>
+      </c>
+      <c r="L147">
+        <v>100</v>
+      </c>
+      <c r="P147" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <v>2026</v>
+      </c>
+      <c r="B148">
+        <v>10</v>
+      </c>
+      <c r="C148" t="s">
+        <v>97</v>
+      </c>
+      <c r="D148" t="s">
+        <v>214</v>
+      </c>
+      <c r="E148" t="s">
+        <v>40</v>
+      </c>
+      <c r="F148" t="s">
+        <v>530</v>
+      </c>
+      <c r="G148" t="s">
+        <v>113</v>
+      </c>
+      <c r="J148" t="s">
+        <v>11</v>
+      </c>
+      <c r="M148">
+        <v>30</v>
+      </c>
+      <c r="P148" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <v>2026</v>
+      </c>
+      <c r="B149">
+        <v>10</v>
+      </c>
+      <c r="C149" t="s">
+        <v>97</v>
+      </c>
+      <c r="D149" t="s">
+        <v>32</v>
+      </c>
+      <c r="E149" t="s">
+        <v>147</v>
+      </c>
+      <c r="F149" t="s">
+        <v>532</v>
+      </c>
+      <c r="G149" t="s">
+        <v>113</v>
+      </c>
+      <c r="J149" t="s">
+        <v>11</v>
+      </c>
+      <c r="M149">
+        <v>20</v>
+      </c>
+      <c r="P149" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <v>2026</v>
+      </c>
+      <c r="B150">
+        <v>10</v>
+      </c>
+      <c r="C150" t="s">
+        <v>97</v>
+      </c>
+      <c r="D150" t="s">
+        <v>29</v>
+      </c>
+      <c r="E150" t="s">
+        <v>41</v>
+      </c>
+      <c r="F150" t="s">
+        <v>49</v>
+      </c>
+      <c r="G150" t="s">
+        <v>263</v>
+      </c>
+      <c r="I150" t="s">
+        <v>192</v>
+      </c>
+      <c r="J150" t="s">
+        <v>282</v>
+      </c>
+      <c r="P150" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <v>2026</v>
+      </c>
+      <c r="B151">
+        <v>10</v>
+      </c>
+      <c r="C151" t="s">
+        <v>97</v>
+      </c>
+      <c r="D151" t="s">
+        <v>108</v>
+      </c>
+      <c r="E151" t="s">
+        <v>45</v>
+      </c>
+      <c r="F151" t="s">
+        <v>532</v>
+      </c>
+      <c r="G151" t="s">
+        <v>111</v>
+      </c>
+      <c r="H151" t="s">
+        <v>578</v>
+      </c>
+      <c r="J151" t="s">
+        <v>282</v>
+      </c>
+      <c r="P151" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <v>2026</v>
+      </c>
+      <c r="B152">
+        <v>10</v>
+      </c>
+      <c r="C152" t="s">
+        <v>97</v>
+      </c>
+      <c r="D152" t="s">
+        <v>35</v>
+      </c>
+      <c r="E152" t="s">
+        <v>42</v>
+      </c>
+      <c r="F152" t="s">
+        <v>530</v>
+      </c>
+      <c r="G152" t="s">
+        <v>113</v>
+      </c>
+      <c r="J152" t="s">
+        <v>11</v>
+      </c>
+      <c r="M152">
+        <v>10</v>
+      </c>
+      <c r="P152" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <v>2026</v>
+      </c>
+      <c r="B153">
+        <v>10</v>
+      </c>
+      <c r="C153" t="s">
+        <v>97</v>
+      </c>
+      <c r="D153" t="s">
+        <v>36</v>
+      </c>
+      <c r="E153" t="s">
+        <v>45</v>
+      </c>
+      <c r="F153" t="s">
+        <v>49</v>
+      </c>
+      <c r="G153" t="s">
+        <v>233</v>
+      </c>
+      <c r="H153" t="s">
+        <v>579</v>
+      </c>
+      <c r="J153" t="s">
+        <v>81</v>
+      </c>
+      <c r="O153" t="s">
+        <v>136</v>
+      </c>
+      <c r="P153" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <v>2026</v>
+      </c>
+      <c r="B154">
+        <v>10</v>
+      </c>
+      <c r="C154" t="s">
+        <v>97</v>
+      </c>
+      <c r="D154" t="s">
+        <v>27</v>
+      </c>
+      <c r="E154" t="s">
+        <v>503</v>
+      </c>
+      <c r="F154" t="s">
+        <v>530</v>
+      </c>
+      <c r="G154" t="s">
+        <v>111</v>
+      </c>
+      <c r="H154" t="s">
+        <v>578</v>
+      </c>
+      <c r="J154" t="s">
+        <v>81</v>
+      </c>
+      <c r="O154" t="s">
+        <v>580</v>
+      </c>
+      <c r="P154" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>2026</v>
+      </c>
+      <c r="B155">
+        <v>10</v>
+      </c>
+      <c r="C155" t="s">
+        <v>97</v>
+      </c>
+      <c r="D155" t="s">
+        <v>29</v>
+      </c>
+      <c r="E155" t="s">
+        <v>41</v>
+      </c>
+      <c r="F155" t="s">
+        <v>531</v>
+      </c>
+      <c r="G155" t="s">
+        <v>119</v>
+      </c>
+      <c r="H155" t="s">
+        <v>581</v>
+      </c>
+      <c r="J155" t="s">
+        <v>10</v>
+      </c>
+      <c r="L155">
+        <v>5000</v>
+      </c>
+      <c r="P155" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>2026</v>
+      </c>
+      <c r="B156">
+        <v>10</v>
+      </c>
+      <c r="C156" t="s">
+        <v>97</v>
+      </c>
+      <c r="D156" t="s">
+        <v>24</v>
+      </c>
+      <c r="E156" t="s">
+        <v>41</v>
+      </c>
+      <c r="F156" t="s">
+        <v>49</v>
+      </c>
+      <c r="G156" t="s">
+        <v>233</v>
+      </c>
+      <c r="H156" t="s">
+        <v>582</v>
+      </c>
+      <c r="J156" t="s">
+        <v>10</v>
+      </c>
+      <c r="L156">
+        <v>30000</v>
+      </c>
+      <c r="O156" t="s">
+        <v>583</v>
+      </c>
+      <c r="P156" t="s">
+        <v>574</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3280" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{832C8B2E-156E-4BF4-85BC-8E9ED21AE32E}"/>
+  <xr:revisionPtr revIDLastSave="3395" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA451457-1A06-4F93-8E81-14DCC6CC6A56}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11622" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11719" uniqueCount="588">
   <si>
     <t>Year</t>
   </si>
@@ -1778,6 +1778,18 @@
   </si>
   <si>
     <t>10000 of fine is suspended for 12 months</t>
+  </si>
+  <si>
+    <t>Out of position at safety car line during the formation lap</t>
+  </si>
+  <si>
+    <t>Garry Connelly, Matthew Selley, Richa Mergulhao, Vitantonio Liuzzi, Istvan Moni</t>
+  </si>
+  <si>
+    <t>Paul Aron</t>
+  </si>
+  <si>
+    <t>Grid Penalty, Penalty Point</t>
   </si>
 </sst>
 </file>
@@ -45922,7 +45934,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P156"/>
+  <dimension ref="A1:P169"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -51085,6 +51097,422 @@
         <v>574</v>
       </c>
     </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <v>2026</v>
+      </c>
+      <c r="B157">
+        <v>11</v>
+      </c>
+      <c r="C157" t="s">
+        <v>93</v>
+      </c>
+      <c r="D157" t="s">
+        <v>23</v>
+      </c>
+      <c r="E157" t="s">
+        <v>509</v>
+      </c>
+      <c r="F157" t="s">
+        <v>49</v>
+      </c>
+      <c r="G157" t="s">
+        <v>120</v>
+      </c>
+      <c r="H157" t="s">
+        <v>584</v>
+      </c>
+      <c r="J157" t="s">
+        <v>88</v>
+      </c>
+      <c r="P157" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <v>2026</v>
+      </c>
+      <c r="B158">
+        <v>11</v>
+      </c>
+      <c r="C158" t="s">
+        <v>93</v>
+      </c>
+      <c r="D158" t="s">
+        <v>23</v>
+      </c>
+      <c r="E158" t="s">
+        <v>509</v>
+      </c>
+      <c r="F158" t="s">
+        <v>48</v>
+      </c>
+      <c r="G158" t="s">
+        <v>66</v>
+      </c>
+      <c r="J158" t="s">
+        <v>11</v>
+      </c>
+      <c r="M158" t="s">
+        <v>242</v>
+      </c>
+      <c r="P158" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <v>2026</v>
+      </c>
+      <c r="B159">
+        <v>11</v>
+      </c>
+      <c r="C159" t="s">
+        <v>93</v>
+      </c>
+      <c r="D159" t="s">
+        <v>214</v>
+      </c>
+      <c r="E159" t="s">
+        <v>40</v>
+      </c>
+      <c r="F159" t="s">
+        <v>530</v>
+      </c>
+      <c r="G159" t="s">
+        <v>270</v>
+      </c>
+      <c r="J159" t="s">
+        <v>10</v>
+      </c>
+      <c r="L159">
+        <v>400</v>
+      </c>
+      <c r="P159" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <v>2026</v>
+      </c>
+      <c r="B160">
+        <v>11</v>
+      </c>
+      <c r="C160" t="s">
+        <v>93</v>
+      </c>
+      <c r="D160" t="s">
+        <v>108</v>
+      </c>
+      <c r="E160" t="s">
+        <v>45</v>
+      </c>
+      <c r="F160" t="s">
+        <v>530</v>
+      </c>
+      <c r="G160" t="s">
+        <v>264</v>
+      </c>
+      <c r="I160" t="s">
+        <v>586</v>
+      </c>
+      <c r="J160" t="s">
+        <v>282</v>
+      </c>
+      <c r="P160" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <v>2026</v>
+      </c>
+      <c r="B161">
+        <v>11</v>
+      </c>
+      <c r="C161" t="s">
+        <v>93</v>
+      </c>
+      <c r="D161" t="s">
+        <v>259</v>
+      </c>
+      <c r="E161" t="s">
+        <v>38</v>
+      </c>
+      <c r="F161" t="s">
+        <v>48</v>
+      </c>
+      <c r="G161" t="s">
+        <v>275</v>
+      </c>
+      <c r="J161" t="s">
+        <v>88</v>
+      </c>
+      <c r="P161" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <v>2026</v>
+      </c>
+      <c r="B162">
+        <v>11</v>
+      </c>
+      <c r="C162" t="s">
+        <v>93</v>
+      </c>
+      <c r="D162" t="s">
+        <v>259</v>
+      </c>
+      <c r="E162" t="s">
+        <v>38</v>
+      </c>
+      <c r="F162" t="s">
+        <v>48</v>
+      </c>
+      <c r="G162" t="s">
+        <v>111</v>
+      </c>
+      <c r="J162" t="s">
+        <v>587</v>
+      </c>
+      <c r="M162">
+        <v>3</v>
+      </c>
+      <c r="N162">
+        <v>1</v>
+      </c>
+      <c r="P162" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <v>2026</v>
+      </c>
+      <c r="B163">
+        <v>11</v>
+      </c>
+      <c r="C163" t="s">
+        <v>93</v>
+      </c>
+      <c r="D163" t="s">
+        <v>24</v>
+      </c>
+      <c r="E163" t="s">
+        <v>41</v>
+      </c>
+      <c r="F163" t="s">
+        <v>48</v>
+      </c>
+      <c r="G163" t="s">
+        <v>53</v>
+      </c>
+      <c r="I163" t="s">
+        <v>192</v>
+      </c>
+      <c r="J163" t="s">
+        <v>11</v>
+      </c>
+      <c r="M163">
+        <v>3</v>
+      </c>
+      <c r="P163" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <v>2026</v>
+      </c>
+      <c r="B164">
+        <v>11</v>
+      </c>
+      <c r="C164" t="s">
+        <v>93</v>
+      </c>
+      <c r="D164" t="s">
+        <v>24</v>
+      </c>
+      <c r="E164" t="s">
+        <v>41</v>
+      </c>
+      <c r="F164" t="s">
+        <v>49</v>
+      </c>
+      <c r="G164" t="s">
+        <v>270</v>
+      </c>
+      <c r="J164" t="s">
+        <v>82</v>
+      </c>
+      <c r="K164">
+        <v>5</v>
+      </c>
+      <c r="P164" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <v>2026</v>
+      </c>
+      <c r="B165">
+        <v>11</v>
+      </c>
+      <c r="C165" t="s">
+        <v>93</v>
+      </c>
+      <c r="D165" t="s">
+        <v>108</v>
+      </c>
+      <c r="E165" t="s">
+        <v>45</v>
+      </c>
+      <c r="F165" t="s">
+        <v>530</v>
+      </c>
+      <c r="G165" t="s">
+        <v>53</v>
+      </c>
+      <c r="I165" t="s">
+        <v>26</v>
+      </c>
+      <c r="J165" t="s">
+        <v>88</v>
+      </c>
+      <c r="P165" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>2026</v>
+      </c>
+      <c r="B166">
+        <v>11</v>
+      </c>
+      <c r="C166" t="s">
+        <v>93</v>
+      </c>
+      <c r="D166" t="s">
+        <v>108</v>
+      </c>
+      <c r="E166" t="s">
+        <v>45</v>
+      </c>
+      <c r="F166" t="s">
+        <v>49</v>
+      </c>
+      <c r="G166" t="s">
+        <v>263</v>
+      </c>
+      <c r="I166" t="s">
+        <v>192</v>
+      </c>
+      <c r="J166" t="s">
+        <v>82</v>
+      </c>
+      <c r="K166">
+        <v>5</v>
+      </c>
+      <c r="P166" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>2026</v>
+      </c>
+      <c r="B167">
+        <v>11</v>
+      </c>
+      <c r="C167" t="s">
+        <v>93</v>
+      </c>
+      <c r="D167" t="s">
+        <v>217</v>
+      </c>
+      <c r="E167" t="s">
+        <v>39</v>
+      </c>
+      <c r="F167" t="s">
+        <v>49</v>
+      </c>
+      <c r="G167" t="s">
+        <v>313</v>
+      </c>
+      <c r="J167" t="s">
+        <v>82</v>
+      </c>
+      <c r="K167">
+        <v>5</v>
+      </c>
+      <c r="P167" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <v>2026</v>
+      </c>
+      <c r="B168">
+        <v>11</v>
+      </c>
+      <c r="C168" t="s">
+        <v>93</v>
+      </c>
+      <c r="D168" t="s">
+        <v>29</v>
+      </c>
+      <c r="E168" t="s">
+        <v>41</v>
+      </c>
+      <c r="F168" t="s">
+        <v>49</v>
+      </c>
+      <c r="G168" t="s">
+        <v>111</v>
+      </c>
+      <c r="J168" t="s">
+        <v>282</v>
+      </c>
+      <c r="P168" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <v>2026</v>
+      </c>
+      <c r="B169">
+        <v>11</v>
+      </c>
+      <c r="C169" t="s">
+        <v>93</v>
+      </c>
+      <c r="D169" t="s">
+        <v>26</v>
+      </c>
+      <c r="E169" t="s">
+        <v>40</v>
+      </c>
+      <c r="F169" t="s">
+        <v>530</v>
+      </c>
+      <c r="G169" t="s">
+        <v>264</v>
+      </c>
+      <c r="J169" t="s">
+        <v>282</v>
+      </c>
+      <c r="P169" t="s">
+        <v>585</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/F1Penalties.xlsx
+++ b/data/F1Penalties.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0ff7b57b908ca8/Desktop/F1 Notebooks/penaltyDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3395" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA451457-1A06-4F93-8E81-14DCC6CC6A56}"/>
+  <xr:revisionPtr revIDLastSave="3574" documentId="8_{37F5A6FD-68A1-49CA-8A46-44A4063429BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E290930-91BE-42F0-BAA7-95394AAE42F6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11719" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11866" uniqueCount="595">
   <si>
     <t>Year</t>
   </si>
@@ -1790,6 +1790,27 @@
   </si>
   <si>
     <t>Grid Penalty, Penalty Point</t>
+  </si>
+  <si>
+    <t>Felix Holter, Mathieu Rommerie, Tomas Kunac, Vitantonio Liuzzi, Stijn Drinkenburg</t>
+  </si>
+  <si>
+    <t>Stopped before Safety Car Line 1</t>
+  </si>
+  <si>
+    <t>Red Light at Pit Exit</t>
+  </si>
+  <si>
+    <t>Driver's First Reprimand of the the season</t>
+  </si>
+  <si>
+    <t>Failure to slow for single yellow</t>
+  </si>
+  <si>
+    <t>Overtaking under double yellow</t>
+  </si>
+  <si>
+    <t>Left the pit lane when the light at the end of the pit lane was red</t>
   </si>
 </sst>
 </file>
@@ -45934,7 +45955,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FB3B3F-BE36-420E-A20B-01EC910651FC}">
-  <dimension ref="A1:P169"/>
+  <dimension ref="A1:P187"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="32.21875" customWidth="1"/>
@@ -51513,6 +51534,612 @@
         <v>585</v>
       </c>
     </row>
+    <row r="170" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <v>2026</v>
+      </c>
+      <c r="B170">
+        <v>12</v>
+      </c>
+      <c r="C170" t="s">
+        <v>140</v>
+      </c>
+      <c r="D170" t="s">
+        <v>25</v>
+      </c>
+      <c r="E170" t="s">
+        <v>149</v>
+      </c>
+      <c r="F170" t="s">
+        <v>48</v>
+      </c>
+      <c r="G170" t="s">
+        <v>233</v>
+      </c>
+      <c r="I170" t="s">
+        <v>260</v>
+      </c>
+      <c r="J170" t="s">
+        <v>282</v>
+      </c>
+      <c r="P170" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <v>2026</v>
+      </c>
+      <c r="B171">
+        <v>12</v>
+      </c>
+      <c r="C171" t="s">
+        <v>140</v>
+      </c>
+      <c r="D171" t="s">
+        <v>26</v>
+      </c>
+      <c r="E171" t="s">
+        <v>40</v>
+      </c>
+      <c r="F171" t="s">
+        <v>174</v>
+      </c>
+      <c r="G171" t="s">
+        <v>122</v>
+      </c>
+      <c r="H171" t="s">
+        <v>589</v>
+      </c>
+      <c r="J171" t="s">
+        <v>282</v>
+      </c>
+      <c r="P171" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <v>2026</v>
+      </c>
+      <c r="B172">
+        <v>12</v>
+      </c>
+      <c r="C172" t="s">
+        <v>140</v>
+      </c>
+      <c r="D172" t="s">
+        <v>260</v>
+      </c>
+      <c r="E172" t="s">
+        <v>503</v>
+      </c>
+      <c r="F172" t="s">
+        <v>49</v>
+      </c>
+      <c r="G172" t="s">
+        <v>120</v>
+      </c>
+      <c r="H172" t="s">
+        <v>590</v>
+      </c>
+      <c r="J172" t="s">
+        <v>81</v>
+      </c>
+      <c r="O172" t="s">
+        <v>591</v>
+      </c>
+      <c r="P172" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <v>2026</v>
+      </c>
+      <c r="B173">
+        <v>12</v>
+      </c>
+      <c r="C173" t="s">
+        <v>140</v>
+      </c>
+      <c r="D173" t="s">
+        <v>260</v>
+      </c>
+      <c r="E173" t="s">
+        <v>503</v>
+      </c>
+      <c r="F173" t="s">
+        <v>174</v>
+      </c>
+      <c r="G173" t="s">
+        <v>233</v>
+      </c>
+      <c r="I173" t="s">
+        <v>217</v>
+      </c>
+      <c r="J173" t="s">
+        <v>88</v>
+      </c>
+      <c r="P173" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <v>2026</v>
+      </c>
+      <c r="B174">
+        <v>12</v>
+      </c>
+      <c r="C174" t="s">
+        <v>140</v>
+      </c>
+      <c r="D174" t="s">
+        <v>23</v>
+      </c>
+      <c r="E174" t="s">
+        <v>509</v>
+      </c>
+      <c r="F174" t="s">
+        <v>48</v>
+      </c>
+      <c r="G174" t="s">
+        <v>66</v>
+      </c>
+      <c r="J174" t="s">
+        <v>11</v>
+      </c>
+      <c r="M174" t="s">
+        <v>242</v>
+      </c>
+      <c r="P174" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <v>2026</v>
+      </c>
+      <c r="B175">
+        <v>12</v>
+      </c>
+      <c r="C175" t="s">
+        <v>140</v>
+      </c>
+      <c r="D175" t="s">
+        <v>32</v>
+      </c>
+      <c r="E175" t="s">
+        <v>147</v>
+      </c>
+      <c r="F175" t="s">
+        <v>150</v>
+      </c>
+      <c r="G175" t="s">
+        <v>66</v>
+      </c>
+      <c r="J175" t="s">
+        <v>11</v>
+      </c>
+      <c r="M175" t="s">
+        <v>242</v>
+      </c>
+      <c r="P175" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <v>2026</v>
+      </c>
+      <c r="B176">
+        <v>12</v>
+      </c>
+      <c r="C176" t="s">
+        <v>140</v>
+      </c>
+      <c r="D176" t="s">
+        <v>28</v>
+      </c>
+      <c r="E176" t="s">
+        <v>147</v>
+      </c>
+      <c r="F176" t="s">
+        <v>174</v>
+      </c>
+      <c r="G176" t="s">
+        <v>122</v>
+      </c>
+      <c r="H176" t="s">
+        <v>589</v>
+      </c>
+      <c r="J176" t="s">
+        <v>282</v>
+      </c>
+      <c r="P176" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <v>2026</v>
+      </c>
+      <c r="B177">
+        <v>12</v>
+      </c>
+      <c r="C177" t="s">
+        <v>140</v>
+      </c>
+      <c r="D177" t="s">
+        <v>143</v>
+      </c>
+      <c r="E177" t="s">
+        <v>262</v>
+      </c>
+      <c r="F177" t="s">
+        <v>174</v>
+      </c>
+      <c r="G177" t="s">
+        <v>122</v>
+      </c>
+      <c r="H177" t="s">
+        <v>589</v>
+      </c>
+      <c r="J177" t="s">
+        <v>282</v>
+      </c>
+      <c r="P177" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <v>2026</v>
+      </c>
+      <c r="B178">
+        <v>12</v>
+      </c>
+      <c r="C178" t="s">
+        <v>140</v>
+      </c>
+      <c r="D178" t="s">
+        <v>194</v>
+      </c>
+      <c r="E178" t="s">
+        <v>40</v>
+      </c>
+      <c r="F178" t="s">
+        <v>49</v>
+      </c>
+      <c r="G178" t="s">
+        <v>111</v>
+      </c>
+      <c r="J178" t="s">
+        <v>80</v>
+      </c>
+      <c r="K178">
+        <v>10</v>
+      </c>
+      <c r="N178">
+        <v>1</v>
+      </c>
+      <c r="O178" t="s">
+        <v>592</v>
+      </c>
+      <c r="P178" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <v>2026</v>
+      </c>
+      <c r="B179">
+        <v>12</v>
+      </c>
+      <c r="C179" t="s">
+        <v>140</v>
+      </c>
+      <c r="D179" t="s">
+        <v>328</v>
+      </c>
+      <c r="E179" t="s">
+        <v>262</v>
+      </c>
+      <c r="F179" t="s">
+        <v>49</v>
+      </c>
+      <c r="G179" t="s">
+        <v>111</v>
+      </c>
+      <c r="I179" t="s">
+        <v>25</v>
+      </c>
+      <c r="J179" t="s">
+        <v>317</v>
+      </c>
+      <c r="N179">
+        <v>2</v>
+      </c>
+      <c r="O179" t="s">
+        <v>593</v>
+      </c>
+      <c r="P179" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <v>2026</v>
+      </c>
+      <c r="B180">
+        <v>12</v>
+      </c>
+      <c r="C180" t="s">
+        <v>140</v>
+      </c>
+      <c r="D180" t="s">
+        <v>215</v>
+      </c>
+      <c r="E180" t="s">
+        <v>149</v>
+      </c>
+      <c r="F180" t="s">
+        <v>49</v>
+      </c>
+      <c r="G180" t="s">
+        <v>111</v>
+      </c>
+      <c r="J180" t="s">
+        <v>80</v>
+      </c>
+      <c r="K180">
+        <v>10</v>
+      </c>
+      <c r="N180">
+        <v>1</v>
+      </c>
+      <c r="O180" t="s">
+        <v>592</v>
+      </c>
+      <c r="P180" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <v>2026</v>
+      </c>
+      <c r="B181">
+        <v>12</v>
+      </c>
+      <c r="C181" t="s">
+        <v>140</v>
+      </c>
+      <c r="D181" t="s">
+        <v>215</v>
+      </c>
+      <c r="E181" t="s">
+        <v>149</v>
+      </c>
+      <c r="F181" t="s">
+        <v>49</v>
+      </c>
+      <c r="G181" t="s">
+        <v>111</v>
+      </c>
+      <c r="I181" t="s">
+        <v>143</v>
+      </c>
+      <c r="J181" t="s">
+        <v>317</v>
+      </c>
+      <c r="N181">
+        <v>2</v>
+      </c>
+      <c r="O181" t="s">
+        <v>593</v>
+      </c>
+      <c r="P181" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <v>2026</v>
+      </c>
+      <c r="B182">
+        <v>12</v>
+      </c>
+      <c r="C182" t="s">
+        <v>140</v>
+      </c>
+      <c r="D182" t="s">
+        <v>24</v>
+      </c>
+      <c r="E182" t="s">
+        <v>41</v>
+      </c>
+      <c r="F182" t="s">
+        <v>174</v>
+      </c>
+      <c r="G182" t="s">
+        <v>122</v>
+      </c>
+      <c r="H182" t="s">
+        <v>589</v>
+      </c>
+      <c r="J182" t="s">
+        <v>282</v>
+      </c>
+      <c r="P182" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <v>2026</v>
+      </c>
+      <c r="B183">
+        <v>12</v>
+      </c>
+      <c r="C183" t="s">
+        <v>140</v>
+      </c>
+      <c r="D183" t="s">
+        <v>108</v>
+      </c>
+      <c r="E183" t="s">
+        <v>45</v>
+      </c>
+      <c r="F183" t="s">
+        <v>150</v>
+      </c>
+      <c r="G183" t="s">
+        <v>66</v>
+      </c>
+      <c r="J183" t="s">
+        <v>11</v>
+      </c>
+      <c r="M183" t="s">
+        <v>242</v>
+      </c>
+      <c r="P183" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <v>2026</v>
+      </c>
+      <c r="B184">
+        <v>12</v>
+      </c>
+      <c r="C184" t="s">
+        <v>140</v>
+      </c>
+      <c r="D184" t="s">
+        <v>108</v>
+      </c>
+      <c r="E184" t="s">
+        <v>45</v>
+      </c>
+      <c r="F184" t="s">
+        <v>49</v>
+      </c>
+      <c r="G184" t="s">
+        <v>263</v>
+      </c>
+      <c r="I184" t="s">
+        <v>36</v>
+      </c>
+      <c r="J184" t="s">
+        <v>82</v>
+      </c>
+      <c r="K184">
+        <v>10</v>
+      </c>
+      <c r="P184" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <v>2026</v>
+      </c>
+      <c r="B185">
+        <v>12</v>
+      </c>
+      <c r="C185" t="s">
+        <v>140</v>
+      </c>
+      <c r="D185" t="s">
+        <v>463</v>
+      </c>
+      <c r="E185" t="s">
+        <v>509</v>
+      </c>
+      <c r="F185" t="s">
+        <v>174</v>
+      </c>
+      <c r="G185" t="s">
+        <v>122</v>
+      </c>
+      <c r="H185" t="s">
+        <v>589</v>
+      </c>
+      <c r="J185" t="s">
+        <v>282</v>
+      </c>
+      <c r="P185" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <v>2026</v>
+      </c>
+      <c r="B186">
+        <v>12</v>
+      </c>
+      <c r="C186" t="s">
+        <v>140</v>
+      </c>
+      <c r="D186" t="s">
+        <v>217</v>
+      </c>
+      <c r="E186" t="s">
+        <v>39</v>
+      </c>
+      <c r="F186" t="s">
+        <v>49</v>
+      </c>
+      <c r="G186" t="s">
+        <v>120</v>
+      </c>
+      <c r="H186" t="s">
+        <v>594</v>
+      </c>
+      <c r="J186" t="s">
+        <v>81</v>
+      </c>
+      <c r="O186" t="s">
+        <v>543</v>
+      </c>
+      <c r="P186" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <v>2026</v>
+      </c>
+      <c r="B187">
+        <v>12</v>
+      </c>
+      <c r="C187" t="s">
+        <v>140</v>
+      </c>
+      <c r="D187" t="s">
+        <v>108</v>
+      </c>
+      <c r="E187" t="s">
+        <v>45</v>
+      </c>
+      <c r="F187" t="s">
+        <v>150</v>
+      </c>
+      <c r="G187" t="s">
+        <v>275</v>
+      </c>
+      <c r="J187" t="s">
+        <v>88</v>
+      </c>
+      <c r="P187" t="s">
+        <v>588</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
